--- a/projects/dm-treatment-algorithm.xlsx
+++ b/projects/dm-treatment-algorithm.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection workbookPassword="A80F" lockStructure="1"/>
+  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -98,6 +98,29 @@
       <family val="2"/>
       <b val="1"/>
       <color rgb="FF1F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF1A1A1A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -750,10 +773,13 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
@@ -778,7 +804,16 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -788,7 +823,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -806,7 +841,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -819,31 +854,31 @@
     <xf numFmtId="2" fontId="10" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -855,7 +890,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -870,16 +905,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -889,25 +924,25 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -919,16 +954,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -937,19 +972,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -958,7 +993,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -968,7 +1003,7 @@
     <xf numFmtId="0" fontId="8" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -977,7 +1012,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1014,7 +1049,16 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1024,7 +1068,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1043,7 +1087,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1056,31 +1100,31 @@
     <xf numFmtId="2" fontId="10" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1089,7 +1133,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1104,14 +1148,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1121,23 +1165,23 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1152,17 +1196,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1171,26 +1215,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1201,7 +1247,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1215,7 +1261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1224,7 +1270,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1497,243 +1543,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66796875" defaultRowHeight="15.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="14" customWidth="1" style="76" min="1" max="1"/>
-    <col width="92" customWidth="1" style="76" min="2" max="2"/>
+    <col width="14" customWidth="1" style="80" min="1" max="1"/>
+    <col width="92" customWidth="1" style="80" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="77">
-      <c r="A1" s="78" t="inlineStr">
+    <row r="1" ht="25.5" customHeight="1" s="81">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>Diabetes Treatment Algorithm — Instructions</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" s="77">
-      <c r="A2" s="79" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="81">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>Read this page before using the tool. Tabs are listed in the order you'll typically use them.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="77">
-      <c r="A4" s="80" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="81">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>Instructions for Patient Information Worksheet</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="27.75" customHeight="1" s="77">
-      <c r="A5" s="81" t="n">
+    <row r="5" ht="27.75" customHeight="1" s="81">
+      <c r="A5" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="82" t="inlineStr">
+      <c r="B5" s="86" t="inlineStr">
         <is>
           <t>Enter all patient parameters in the fields outlined in red (age, gender, weight, height, serum creatinine).</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="27.75" customHeight="1" s="77">
-      <c r="A6" s="81" t="n">
+    <row r="6" ht="27.75" customHeight="1" s="81">
+      <c r="A6" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t>Select Yes/No for each Medical History item, including the new Obesity/overweight flag — these drive the preferred-therapy recommendations on the DM Medications tab.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="27.75" customHeight="1" s="77">
-      <c r="A7" s="81" t="n">
+    <row r="7" ht="27.75" customHeight="1" s="81">
+      <c r="A7" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="82" t="inlineStr">
+      <c r="B7" s="86" t="inlineStr">
         <is>
           <t>Calculated values (Ideal/Adjusted Body Weight, BMI, CrCl, eGFR) populate automatically in blue — no need to enter these.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="9.75" customHeight="1" s="77"/>
-    <row r="9" ht="18" customHeight="1" s="77">
-      <c r="A9" s="80" t="inlineStr">
+    <row r="8" ht="9.75" customHeight="1" s="81"/>
+    <row r="9" ht="18" customHeight="1" s="81">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>Instructions for DM Medications Worksheet</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="27.75" customHeight="1" s="77">
-      <c r="A10" s="81" t="n">
+    <row r="10" ht="27.75" customHeight="1" s="81">
+      <c r="A10" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="86" t="inlineStr">
         <is>
           <t>Use the cardiorenal risk / comorbidity table to identify preferred therapy based on the history entered on the Patient Information tab (ASCVD, heart failure, CKD, obesity, MASLD/MASH).</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="27.75" customHeight="1" s="77">
-      <c r="A11" s="81" t="n">
+    <row r="11" ht="27.75" customHeight="1" s="81">
+      <c r="A11" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="82" t="inlineStr">
+      <c r="B11" s="86" t="inlineStr">
         <is>
           <t>Select an oral and/or injectable drug of choice from the red dropdown fields; dosing populates automatically in blue.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="27.75" customHeight="1" s="77">
-      <c r="A12" s="81" t="n">
+    <row r="12" ht="27.75" customHeight="1" s="81">
+      <c r="A12" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="82" t="inlineStr">
+      <c r="B12" s="86" t="inlineStr">
         <is>
           <t>Reassess therapy, including the need for hypoglycemia-prone agents, every 3-6 months.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="9.75" customHeight="1" s="77"/>
-    <row r="14" ht="18" customHeight="1" s="77">
-      <c r="A14" s="80" t="inlineStr">
+    <row r="13" ht="9.75" customHeight="1" s="81"/>
+    <row r="14" ht="18" customHeight="1" s="81">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>Instructions for Insulin Worksheet</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="27.75" customHeight="1" s="77">
-      <c r="A15" s="81" t="n">
+    <row r="15" ht="27.75" customHeight="1" s="81">
+      <c r="A15" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="82" t="inlineStr">
+      <c r="B15" s="86" t="inlineStr">
         <is>
           <t>Use the initial dosing section to calculate starting insulin doses from patient weight (pulled automatically from Patient Information).</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="27.75" customHeight="1" s="77">
-      <c r="A16" s="81" t="n">
+    <row r="16" ht="27.75" customHeight="1" s="81">
+      <c r="A16" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="86" t="inlineStr">
         <is>
           <t>Use the Adjusting Insulin Regimen section to calculate correction dose and insulin-to-carb ratio from entered blood glucose values.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="27.75" customHeight="1" s="77">
-      <c r="A17" s="81" t="n">
+    <row r="17" ht="27.75" customHeight="1" s="81">
+      <c r="A17" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="82" t="inlineStr">
+      <c r="B17" s="86" t="inlineStr">
         <is>
           <t>Use the Insulin Conversions section when switching between insulin products, including the new once-weekly insulin icodec (Awiqli) calculator.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="9.75" customHeight="1" s="77"/>
-    <row r="19" ht="18" customHeight="1" s="77">
-      <c r="A19" s="80" t="inlineStr">
+    <row r="18" ht="9.75" customHeight="1" s="81"/>
+    <row r="19" ht="18" customHeight="1" s="81">
+      <c r="A19" s="84" t="inlineStr">
         <is>
           <t>Instructions for SMBG Worksheet</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="27.75" customHeight="1" s="77">
-      <c r="A20" s="81" t="n">
+    <row r="20" ht="27.75" customHeight="1" s="81">
+      <c r="A20" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="82" t="inlineStr">
+      <c r="B20" s="86" t="inlineStr">
         <is>
           <t>Enter blood glucose readings in the red grid for each meal time (before/after breakfast, lunch, dinner, and bedtime).</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="27.75" customHeight="1" s="77">
-      <c r="A21" s="81" t="n">
+    <row r="21" ht="27.75" customHeight="1" s="81">
+      <c r="A21" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="82" t="inlineStr">
+      <c r="B21" s="86" t="inlineStr">
         <is>
           <t>Running averages, hypoglycemia count, and hyperglycemia count calculate automatically — hypoglycemic readings (&lt;70) highlight red, readings over 180 highlight purple.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="27.75" customHeight="1" s="77">
-      <c r="A22" s="81" t="n">
+    <row r="22" ht="27.75" customHeight="1" s="81">
+      <c r="A22" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="82" t="inlineStr">
+      <c r="B22" s="86" t="inlineStr">
         <is>
           <t>Reference current ADA blood sugar goals in the panel on the right, including the 2026 age/frailty-individualized and perioperative targets noted at the bottom of the tab.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="9.75" customHeight="1" s="77"/>
-    <row r="24" ht="19.5" customHeight="1" s="77">
-      <c r="A24" s="83" t="inlineStr">
+    <row r="23" ht="9.75" customHeight="1" s="81"/>
+    <row r="24" ht="19.5" customHeight="1" s="81">
+      <c r="A24" s="87" t="inlineStr">
         <is>
           <t>This tool is intended to support, not replace, clinical judgment. Verify all calculated values and dosing recommendations — especially any field marked new for ADA 2026 — before use in patient care.</t>
         </is>
       </c>
-      <c r="B24" s="84" t="n"/>
-    </row>
-    <row r="25" ht="19.5" customHeight="1" s="77">
-      <c r="A25" s="85" t="n"/>
-    </row>
-    <row r="26" ht="19.5" customHeight="1" s="77">
-      <c r="A26" s="85" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" s="77">
-      <c r="A28" s="86" t="inlineStr">
+      <c r="B24" s="88" t="n"/>
+    </row>
+    <row r="25" ht="19.5" customHeight="1" s="81">
+      <c r="A25" s="89" t="n"/>
+    </row>
+    <row r="26" ht="19.5" customHeight="1" s="81">
+      <c r="A26" s="89" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="81">
+      <c r="A28" s="90" t="inlineStr">
         <is>
           <t>Created by</t>
         </is>
       </c>
-      <c r="B28" s="87" t="inlineStr">
+      <c r="B28" s="91" t="inlineStr">
         <is>
           <t>Andrew Tran, PharmD, BCACP, BCPS</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" s="77">
-      <c r="A29" s="86" t="inlineStr">
+    <row r="29" ht="18" customHeight="1" s="81">
+      <c r="A29" s="90" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B29" s="87" t="inlineStr">
+      <c r="B29" s="91" t="inlineStr">
         <is>
           <t>2.0 — updated to ADA Standards of Care in Diabetes—2026</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1" s="77">
-      <c r="A30" s="86" t="inlineStr">
+    <row r="30" ht="18" customHeight="1" s="81">
+      <c r="A30" s="90" t="inlineStr">
         <is>
           <t>Created on</t>
         </is>
       </c>
-      <c r="B30" s="87" t="inlineStr">
+      <c r="B30" s="91" t="inlineStr">
         <is>
           <t>06/01/2019</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" s="77">
-      <c r="A31" s="86" t="inlineStr">
+    <row r="31" ht="18" customHeight="1" s="81">
+      <c r="A31" s="90" t="inlineStr">
         <is>
           <t>Last edit</t>
         </is>
       </c>
-      <c r="B31" s="87" t="inlineStr">
+      <c r="B31" s="91" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
     </row>
+    <row r="33" ht="15.75" customHeight="1" s="81">
+      <c r="A33" s="92" t="n"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" s="81">
+      <c r="A34" s="93" t="n"/>
+      <c r="B34" s="94" t="n"/>
+    </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="a80f"/>
   <mergeCells count="7">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
@@ -1758,282 +1810,282 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.83984375" defaultRowHeight="24" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="42" customWidth="1" style="88" min="1" max="1"/>
-    <col width="22" customWidth="1" style="88" min="2" max="2"/>
-    <col width="3" customWidth="1" style="88" min="3" max="5"/>
-    <col width="26" customWidth="1" style="88" min="6" max="6"/>
-    <col width="12" customWidth="1" style="88" min="7" max="7"/>
-    <col width="16" customWidth="1" style="88" min="8" max="8"/>
-    <col width="10.84" customWidth="1" style="88" min="9" max="16384"/>
+    <col width="42" customWidth="1" style="95" min="1" max="1"/>
+    <col width="22" customWidth="1" style="95" min="2" max="2"/>
+    <col width="3" customWidth="1" style="95" min="3" max="5"/>
+    <col width="26" customWidth="1" style="95" min="6" max="6"/>
+    <col width="12" customWidth="1" style="95" min="7" max="7"/>
+    <col width="16" customWidth="1" style="95" min="8" max="8"/>
+    <col width="10.84" customWidth="1" style="95" min="9" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="77">
-      <c r="A1" s="89" t="inlineStr">
+    <row r="1" ht="25.5" customHeight="1" s="81">
+      <c r="A1" s="96" t="inlineStr">
         <is>
           <t>Diabetes Treatment Algorithm — Patient Information</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="77">
-      <c r="A2" s="90" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="81">
+      <c r="A2" s="97" t="inlineStr">
         <is>
           <t>Red = enter data here     |     Blue = calculated automatically     |     Green = updated for ADA Standards of Care in Diabetes—2026</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="77">
-      <c r="A3" s="91" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="81">
+      <c r="A3" s="98" t="inlineStr">
         <is>
           <t>Disclaimer: use of this tool does not replace clinical judgment.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="77">
-      <c r="A4" s="92" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="81">
+      <c r="A4" s="99" t="inlineStr">
         <is>
           <t>Input Patient Parameters</t>
         </is>
       </c>
-      <c r="B4" s="93" t="n"/>
-      <c r="F4" s="94" t="inlineStr">
+      <c r="B4" s="100" t="n"/>
+      <c r="F4" s="101" t="inlineStr">
         <is>
           <t>Conversions</t>
         </is>
       </c>
-      <c r="G4" s="95" t="inlineStr">
+      <c r="G4" s="102" t="inlineStr">
         <is>
           <t>Enter</t>
         </is>
       </c>
-      <c r="H4" s="96" t="inlineStr">
+      <c r="H4" s="103" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="77">
-      <c r="A5" s="97" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1" s="81">
+      <c r="A5" s="104" t="inlineStr">
         <is>
           <t>Patient Age (years)</t>
         </is>
       </c>
-      <c r="B5" s="98" t="n">
+      <c r="B5" s="105" t="n">
         <v>60</v>
       </c>
-      <c r="F5" s="99" t="inlineStr">
+      <c r="F5" s="106" t="inlineStr">
         <is>
           <t>Enter lbs to convert to Kg</t>
         </is>
       </c>
-      <c r="G5" s="98" t="n"/>
-      <c r="H5" s="100">
+      <c r="G5" s="105" t="n"/>
+      <c r="H5" s="107">
         <f>IF(G5="", "", G5/2.2)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="77">
-      <c r="A6" s="97" t="inlineStr">
+    <row r="6" ht="15.75" customHeight="1" s="81">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>Gender (male, female)</t>
         </is>
       </c>
-      <c r="B6" s="98" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>male</t>
         </is>
       </c>
-      <c r="F6" s="99" t="inlineStr">
+      <c r="F6" s="106" t="inlineStr">
         <is>
           <t>Enter kg to  convert to lbs</t>
         </is>
       </c>
-      <c r="G6" s="98" t="n"/>
-      <c r="H6" s="100">
+      <c r="G6" s="105" t="n"/>
+      <c r="H6" s="107">
         <f>IF(G6="","", G6*2.2)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="77">
-      <c r="A7" s="97" t="inlineStr">
+    <row r="7" ht="15.75" customHeight="1" s="81">
+      <c r="A7" s="104" t="inlineStr">
         <is>
           <t>Total Body Weight (kg)</t>
         </is>
       </c>
-      <c r="B7" s="98" t="n">
+      <c r="B7" s="105" t="n">
         <v>60</v>
       </c>
-      <c r="F7" s="99" t="inlineStr">
+      <c r="F7" s="106" t="inlineStr">
         <is>
           <t>Enter cm to inches</t>
         </is>
       </c>
-      <c r="G7" s="98" t="n"/>
-      <c r="H7" s="100">
+      <c r="G7" s="105" t="n"/>
+      <c r="H7" s="107">
         <f>IF(G7="","", G7/2.54)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="77">
-      <c r="A8" s="97" t="inlineStr">
+    <row r="8" ht="15.75" customHeight="1" s="81">
+      <c r="A8" s="104" t="inlineStr">
         <is>
           <t>Height (in)</t>
         </is>
       </c>
-      <c r="B8" s="98" t="n">
+      <c r="B8" s="105" t="n">
         <v>65</v>
       </c>
-      <c r="F8" s="99" t="inlineStr">
+      <c r="F8" s="106" t="inlineStr">
         <is>
           <t>Enter inches to cm</t>
         </is>
       </c>
-      <c r="G8" s="98" t="n"/>
-      <c r="H8" s="100">
+      <c r="G8" s="105" t="n"/>
+      <c r="H8" s="107">
         <f>IF(G8="","", G8*2.54)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="77">
-      <c r="A9" s="97" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1" s="81">
+      <c r="A9" s="104" t="inlineStr">
         <is>
           <t>Ideal Body Weight (kg)</t>
         </is>
       </c>
-      <c r="B9" s="101">
+      <c r="B9" s="108">
         <f>IF(OR(B6="", B8=""), "", IF(B6="male", (50 + 2.3 * (B8 - 60)), IF(B6="female", (45.5 + 2.3 * (B8 - 60)), "")))</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="77">
-      <c r="A10" s="97" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="81">
+      <c r="A10" s="104" t="inlineStr">
         <is>
           <t>Adjusted Body Weight (kg)</t>
         </is>
       </c>
-      <c r="B10" s="101">
+      <c r="B10" s="108">
         <f>IF(OR(B7="", B9=""), "", B9 + (0.4 * (B7 - B9)))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="77">
-      <c r="A11" s="97" t="inlineStr">
+    <row r="11" ht="15.75" customHeight="1" s="81">
+      <c r="A11" s="104" t="inlineStr">
         <is>
           <t>Patient's BMI (%)</t>
         </is>
       </c>
-      <c r="B11" s="101">
+      <c r="B11" s="108">
         <f>IF(OR(B7="", B8=""), "", B7 / (((B8*2.54) / 100) ^ 2))</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="77">
-      <c r="A12" s="97" t="inlineStr">
+    <row r="12" ht="15.75" customHeight="1" s="81">
+      <c r="A12" s="104" t="inlineStr">
         <is>
           <t>Weight used in CrCl calculation</t>
         </is>
       </c>
-      <c r="B12" s="100">
+      <c r="B12" s="107">
         <f>IF(OR(B7="", B9=""), "", IF(B7&lt;B9, "Actual Body Weight", IF(AND(B7&gt;B9, B7&lt;=(B9*1.3)), "Ideal Body Weight", IF(B7&gt;(B9*1.3), "Adjusted Body Weight", ""))))</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="77">
-      <c r="A13" s="97" t="inlineStr">
+    <row r="13" ht="15.75" customHeight="1" s="81">
+      <c r="A13" s="104" t="inlineStr">
         <is>
           <t>Serum Creatinine (mg/L)</t>
         </is>
       </c>
-      <c r="B13" s="98" t="n">
+      <c r="B13" s="105" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="77">
-      <c r="A14" s="97" t="inlineStr">
+    <row r="14" ht="15.75" customHeight="1" s="81">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>CrCl via Cockcroft-Gault Equation (mL/min)</t>
         </is>
       </c>
-      <c r="B14" s="101">
+      <c r="B14" s="108">
         <f>IF(OR(B5="", B6="", B7="", B9="", B10="", B13=""), "", IF(AND(B7&lt;B9,B6="male"),((140-B5)*B7)/(B13*72),IF(AND(B7&lt;B9,B6="female"),0.85*((140-B5)*B7)/(B13*72),
 IF(AND(B7&lt;=(B9*1.3),B6="male"),((140-B5)*B9)/(B13*72),IF(AND(B7&lt;=(B9*1.3),B6="female"),0.85*((140-B5)*B9)/(B13*72),
 IF(AND(B7&gt;(B9*1.3),B6="male"),((140-B5)*B10)/(B13*72),IF(AND(B7&gt;(B9*1.3),B6="female"),0.85*((140-B5)*B10)/(B13*72),"")))))))</f>
         <v/>
       </c>
-      <c r="C14" s="102" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="77">
-      <c r="A15" s="97" t="inlineStr">
+      <c r="C14" s="109" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="81">
+      <c r="A15" s="104" t="inlineStr">
         <is>
           <t>EGFR (mL/min)</t>
         </is>
       </c>
-      <c r="B15" s="101">
+      <c r="B15" s="108">
         <f>IF(OR(B13="", B6="", B5=""), "", 141 * MIN(B13 / IF(B6="male", 0.9, 0.7), 1) ^ IF(B6="male", -0.411, -0.329) * MAX(B13 / IF(B6="male", 0.9, 0.7), 1) ^ (-1.209) * 0.993 ^ B5)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="77">
-      <c r="A16" s="103" t="n"/>
-      <c r="B16" s="104" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="77">
-      <c r="A17" s="103" t="n"/>
-      <c r="B17" s="105" t="inlineStr">
+    <row r="16" ht="24" customHeight="1" s="81">
+      <c r="A16" s="110" t="n"/>
+      <c r="B16" s="111" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="81">
+      <c r="A17" s="110" t="n"/>
+      <c r="B17" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" s="77">
-      <c r="A18" s="92" t="inlineStr">
+    <row r="18" ht="18" customHeight="1" s="81">
+      <c r="A18" s="99" t="inlineStr">
         <is>
           <t>Medical History  (Yes/No — see DM Medications tab)</t>
         </is>
       </c>
-      <c r="B18" s="93" t="n"/>
-    </row>
-    <row r="19" ht="27.75" customHeight="1" s="77">
-      <c r="A19" s="106" t="inlineStr">
+      <c r="B18" s="100" t="n"/>
+    </row>
+    <row r="19" ht="27.75" customHeight="1" s="81">
+      <c r="A19" s="113" t="inlineStr">
         <is>
           <t>ASCVD (established or high-risk)</t>
         </is>
       </c>
-      <c r="B19" s="98" t="n"/>
-    </row>
-    <row r="20" ht="27.75" customHeight="1" s="77">
-      <c r="A20" s="106" t="inlineStr">
+      <c r="B19" s="105" t="n"/>
+    </row>
+    <row r="20" ht="27.75" customHeight="1" s="81">
+      <c r="A20" s="113" t="inlineStr">
         <is>
           <t>Heart Failure (preserved of reduced EF)</t>
         </is>
       </c>
-      <c r="B20" s="98" t="n"/>
-      <c r="C20" s="107" t="n"/>
-    </row>
-    <row r="21" ht="27.75" customHeight="1" s="77">
-      <c r="A21" s="106" t="inlineStr">
+      <c r="B20" s="105" t="n"/>
+      <c r="C20" s="114" t="n"/>
+    </row>
+    <row r="21" ht="27.75" customHeight="1" s="81">
+      <c r="A21" s="113" t="inlineStr">
         <is>
           <t>Chronic Kidney Disease (eGFR &lt; 60 mL/min and/or UAC &gt; 30 mg/g)</t>
         </is>
       </c>
-      <c r="B21" s="98" t="n"/>
-    </row>
-    <row r="22" ht="27.75" customHeight="1" s="77">
-      <c r="A22" s="108" t="inlineStr">
+      <c r="B21" s="105" t="n"/>
+    </row>
+    <row r="22" ht="27.75" customHeight="1" s="81">
+      <c r="A22" s="115" t="inlineStr">
         <is>
           <t>Obesity / overweight (BMI ≥ 27 kg/m² with comorbidity, or BMI ≥ 30 kg/m²)</t>
         </is>
       </c>
-      <c r="B22" s="98" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" s="77">
-      <c r="A24" s="109" t="inlineStr">
+      <c r="B22" s="105" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="81">
+      <c r="A24" s="116" t="inlineStr">
         <is>
           <t>Source: American Diabetes Association. Standards of Care in Diabetes—2026. Diabetes Care. 2026;49(Suppl 1). Insulin dosing verified against FDA prescribing information (DailyMed), accessed Aug 2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="a80f"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="6">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A3:H3"/>
@@ -2067,34 +2119,34 @@
   <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.83984375" defaultRowHeight="24" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="34" customWidth="1" style="110" min="1" max="1"/>
-    <col width="78" customWidth="1" style="110" min="2" max="2"/>
-    <col width="3" customWidth="1" style="110" min="3" max="4"/>
-    <col width="10.84" customWidth="1" style="110" min="5" max="16384"/>
+    <col width="34" customWidth="1" style="117" min="1" max="1"/>
+    <col width="78" customWidth="1" style="117" min="2" max="2"/>
+    <col width="3" customWidth="1" style="117" min="3" max="4"/>
+    <col width="10.84" customWidth="1" style="117" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="77">
-      <c r="A1" s="78" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="81">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>Type 2 Diabetes Pharmacotherapy</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="77">
-      <c r="A2" s="111" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="81">
+      <c r="A2" s="118" t="inlineStr">
         <is>
           <t>Healthy lifestyle behaviors, self-management education/support, and social determinants of health should be considered in ALL patients.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="159.75" customHeight="1" s="77">
-      <c r="A3" s="82" t="inlineStr">
+    <row r="3" ht="159.75" customHeight="1" s="81">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>First-line pharmacotherapy should be selected based upon patient-specific factors: glycemic management needs, cardiorenal risk, comorbidities, cost, and access. Consider combination pharmacotherapy at initiation if A1C is more than 1.5% above target goal.
 ADA 2026 update: in patients with established/high-risk ASCVD, heart failure, CKD, or obesity, consider an SGLT2 inhibitor and/or GLP-1 RA (or GIP/GLP-1 RA) at or near diagnosis — independent of metformin use or baseline A1C — rather than only as a later add-on.</t>
         </is>
       </c>
-      <c r="B3" s="111" t="inlineStr">
+      <c r="B3" s="118" t="inlineStr">
         <is>
           <t>Consider early insulin initiation with extreme hyperglycemia:
 - Blood glucose &gt; 300 mg/dL
@@ -2103,134 +2155,134 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="77">
-      <c r="A4" s="112" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="81">
+      <c r="A4" s="119" t="inlineStr">
         <is>
           <t>Reassess and modify treatment every 3-6 months.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="77">
-      <c r="A5" s="113" t="n"/>
-      <c r="B5" s="113" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="77">
-      <c r="A6" s="114" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="81">
+      <c r="A5" s="120" t="n"/>
+      <c r="B5" s="120" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="81">
+      <c r="A6" s="121" t="inlineStr">
         <is>
           <t>Select Therapy Based on Cardiorenal Risk / Comorbidity</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="77">
-      <c r="A7" s="115" t="inlineStr">
+    <row r="7" ht="15.75" customHeight="1" s="81">
+      <c r="A7" s="122" t="inlineStr">
         <is>
           <t>Comorbidity / Risk Factor</t>
         </is>
       </c>
-      <c r="B7" s="115" t="inlineStr">
+      <c r="B7" s="122" t="inlineStr">
         <is>
           <t>Preferred Therapy</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="69.75" customHeight="1" s="77">
-      <c r="A8" s="116" t="inlineStr">
+    <row r="8" ht="69.75" customHeight="1" s="81">
+      <c r="A8" s="123" t="inlineStr">
         <is>
           <t>ASCVD (established or high risk)</t>
         </is>
       </c>
-      <c r="B8" s="117" t="inlineStr">
+      <c r="B8" s="124" t="inlineStr">
         <is>
           <t>GLP-1 RA or SGLT2i with proven CVD benefit. Consider initiating at or near diagnosis in high-risk patients, independent of metformin use (ADA 2026).</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="69.75" customHeight="1" s="77">
-      <c r="A9" s="116" t="inlineStr">
+    <row r="9" ht="69.75" customHeight="1" s="81">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>Heart Failure (HFrEF or HFpEF)</t>
         </is>
       </c>
-      <c r="B9" s="117" t="inlineStr">
+      <c r="B9" s="124" t="inlineStr">
         <is>
           <t>SGLT2i with HF benefit preferred (avoid TZDs; avoid saxagliptin). GLP-1 RA with HF benefit, or GIP/GLP-1 RA (tirzepatide), also supported — particularly for HFpEF (ADA 2026, based on SUMMIT trial data; guideline-based, not an FDA cardiovascular-outcome label).</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="69.75" customHeight="1" s="77">
-      <c r="A10" s="116" t="inlineStr">
+    <row r="10" ht="69.75" customHeight="1" s="81">
+      <c r="A10" s="123" t="inlineStr">
         <is>
           <t>Chronic Kidney Disease (eGFR &lt; 60 mL/min and/or UACR &gt; 30 mg/g)</t>
         </is>
       </c>
-      <c r="B10" s="117" t="inlineStr">
+      <c r="B10" s="124" t="inlineStr">
         <is>
           <t>On maximally tolerated ACEi/ARB; SGLT2i with renal benefit. GLP-1 RA now also supported in T2DM with CKD (ADA 2026). Consider adding finerenone (nonsteroidal MRA) for persistent albuminuria (UACR ≥ 100 mg/g, eGFR 30-90) as a three-drug cardiorenal approach (ADA 2026).</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="54.75" customHeight="1" s="77">
-      <c r="A11" s="118" t="inlineStr">
+    <row r="11" ht="54.75" customHeight="1" s="81">
+      <c r="A11" s="125" t="inlineStr">
         <is>
           <t>Obesity / overweight (BMI ≥ 27 kg/m² with comorbidity, or BMI ≥ 30 kg/m²)</t>
         </is>
       </c>
-      <c r="B11" s="119" t="inlineStr">
+      <c r="B11" s="126" t="inlineStr">
         <is>
           <t>GLP-1 RA or GIP/GLP-1 RA (tirzepatide) preferred — prioritize the agent with the greatest weight-loss efficacy the patient can access and tolerate (ADA 2026 expanded indication branch).</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="54.75" customHeight="1" s="77">
-      <c r="A12" s="118" t="inlineStr">
+    <row r="12" ht="54.75" customHeight="1" s="81">
+      <c r="A12" s="125" t="inlineStr">
         <is>
           <t>MASLD / MASH (metabolic dysfunction-associated steatotic liver disease / steatohepatitis)</t>
         </is>
       </c>
-      <c r="B12" s="119" t="inlineStr">
+      <c r="B12" s="126" t="inlineStr">
         <is>
           <t>GLP-1 RA or GIP/GLP-1 RA preferred. Pioglitazone also has evidence in MASH but weigh against weight-gain and heart-failure risk (ADA 2026 expanded indication branch).</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" s="77">
-      <c r="A13" s="113" t="n"/>
-      <c r="B13" s="113" t="n"/>
-    </row>
-    <row r="14" ht="39.75" customHeight="1" s="77">
-      <c r="A14" s="119" t="inlineStr">
+    <row r="13" ht="24" customHeight="1" s="81">
+      <c r="A13" s="120" t="n"/>
+      <c r="B13" s="120" t="n"/>
+    </row>
+    <row r="14" ht="39.75" customHeight="1" s="81">
+      <c r="A14" s="126" t="inlineStr">
         <is>
           <t>New for ADA 2026: reassess the need for, and dose of, hypoglycemia-prone agents (sulfonylureas, meglitinides, insulin) whenever a new glucose-lowering medication is added, to reduce hypoglycemia risk and treatment burden.</t>
         </is>
       </c>
-      <c r="B14" s="120" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" s="77">
-      <c r="A15" s="114" t="inlineStr">
+      <c r="B14" s="127" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="81">
+      <c r="A15" s="121" t="inlineStr">
         <is>
           <t>ORALS</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="77">
-      <c r="A16" s="112" t="inlineStr">
+    <row r="16" ht="15.75" customHeight="1" s="81">
+      <c r="A16" s="119" t="inlineStr">
         <is>
           <t>Oral Drug of Choice?</t>
         </is>
       </c>
-      <c r="B16" s="121" t="inlineStr">
+      <c r="B16" s="128" t="inlineStr">
         <is>
           <t>saxagliptin (Onglyza)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" s="77">
-      <c r="A17" s="112" t="inlineStr">
+    <row r="17" ht="60" customHeight="1" s="81">
+      <c r="A17" s="119" t="inlineStr">
         <is>
           <t>Oral Drug Dosing</t>
         </is>
       </c>
-      <c r="B17" s="122">
+      <c r="B17" s="129">
         <f>IF(B16="metformin","IR: start 500 mg PO daily or BID; ER: start 500 mg PO daily; titrate to 2000 mg daily (or 2550 daily with 850 mg TID)",
 IF(B16="glipizide","start 5 mg PO daily;  doses above 15 mg should be divided BID; max 40 mg daily",
 IF(B16="glimepiride","Start 1-2 mg PO daily; max 8 mg daily",
@@ -2247,90 +2299,90 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="77">
-      <c r="A18" s="112" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="81">
+      <c r="A18" s="119" t="inlineStr">
         <is>
           <t>How Supplied</t>
         </is>
       </c>
-      <c r="B18" s="123" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="77">
-      <c r="A19" s="112" t="inlineStr">
+      <c r="B18" s="130" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="81">
+      <c r="A19" s="119" t="inlineStr">
         <is>
           <t>Renal Dosing</t>
         </is>
       </c>
-      <c r="B19" s="123" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="77">
-      <c r="A20" s="113" t="n"/>
-      <c r="B20" s="124" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" s="77">
-      <c r="A21" s="114" t="inlineStr">
+      <c r="B19" s="130" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="81">
+      <c r="A20" s="120" t="n"/>
+      <c r="B20" s="131" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="81">
+      <c r="A21" s="121" t="inlineStr">
         <is>
           <t>INJECTABLES</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="77">
-      <c r="A22" s="112" t="inlineStr">
+    <row r="22" ht="15.75" customHeight="1" s="81">
+      <c r="A22" s="119" t="inlineStr">
         <is>
           <t>Injectable Drug of Choice?</t>
         </is>
       </c>
-      <c r="B22" s="121" t="inlineStr">
+      <c r="B22" s="128" t="inlineStr">
         <is>
           <t>dulaglutide (Trulicity)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="69.75" customHeight="1" s="77">
-      <c r="A23" s="112" t="inlineStr">
+    <row r="23" ht="69.75" customHeight="1" s="81">
+      <c r="A23" s="119" t="inlineStr">
         <is>
           <t>Injectable Drug Dosing</t>
         </is>
       </c>
-      <c r="B23" s="122">
+      <c r="B23" s="129">
         <f>IF(B22="liraglutide (Victoza)","Start 0.6 mg SQ once daily x1 week (not for glycemic control); increase to 1.2 mg once daily; may increase to max 1.8 mg once daily if needed",IF(B22="dulaglutide (Trulicity)","Start 0.75 mg SQ once weekly; may increase to 1.5 mg weekly after at least 4 weeks; if additional control needed, may increase to 3 mg weekly, then 4.5 mg weekly (each after at least 4 weeks on prior dose); max 4.5 mg weekly",IF(B22="exenatide (Byetta)","Start 5 mcg SQ twice daily within 60 minutes before morning and evening meals; after 1 month, may increase to 10 mcg SQ twice daily",IF(B22="exenatide ER (Bydureon)","2 mg SQ once weekly, any time of day, with or without meals",IF(B22="semaglutide (Ozempic)","Start 0.25 mg SQ once weekly x4 weeks (not for glycemic control); increase to 0.5 mg weekly; may increase to 1 mg weekly after at least 4 weeks; if additional control needed, may increase to max 2 mg weekly after at least 4 weeks on 1 mg",IF(B22="tirzepatide (Mounjaro)","Start 2.5 mg SQ once weekly x4 weeks (not for glycemic control); increase to 5 mg weekly; may increase in 2.5 mg increments after at least 4 weeks on current dose; max 15 mg weekly",IF(B22="pramlintide (SymlinPen)","Adjunct to mealtime insulin: start 60 mcg SQ immediately before major meals; may increase to 120 mcg as tolerated. Reduce prandial insulin doses by 50% when initiating to reduce hypoglycemia risk.","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="77">
-      <c r="A24" s="112" t="inlineStr">
+    <row r="24" ht="15.75" customHeight="1" s="81">
+      <c r="A24" s="119" t="inlineStr">
         <is>
           <t>How Supplied</t>
         </is>
       </c>
-      <c r="B24" s="123" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="77">
-      <c r="A25" s="112" t="inlineStr">
+      <c r="B24" s="130" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="81">
+      <c r="A25" s="119" t="inlineStr">
         <is>
           <t>Renal Dosing</t>
         </is>
       </c>
-      <c r="B25" s="123" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" s="77">
-      <c r="A26" s="113" t="n"/>
-      <c r="B26" s="113" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="77">
-      <c r="A27" s="114" t="inlineStr">
+      <c r="B25" s="130" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" s="81">
+      <c r="A26" s="120" t="n"/>
+      <c r="B26" s="120" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="81">
+      <c r="A27" s="121" t="inlineStr">
         <is>
           <t>FIRST-LINE THERAPY: METFORMIN</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="144.75" customHeight="1" s="77">
-      <c r="A28" s="112" t="inlineStr">
+    <row r="28" ht="144.75" customHeight="1" s="81">
+      <c r="A28" s="119" t="inlineStr">
         <is>
           <t>Dosage</t>
         </is>
       </c>
-      <c r="B28" s="111" t="inlineStr">
+      <c r="B28" s="118" t="inlineStr">
         <is>
           <t>- Initial, 500 mg orally twice daily OR 850 mg orally once daily with meals; may adjust dose in 500 mg increments weekly OR 850 mg every 2 weeks; if desired, patients initiated at 500 mg twice daily may be switched to 850 mg twice daily after 2 weeks; MAX dose, 2550 mg/day; max effective dose: 2000 mg daily. Doses greater than 2000 mg/day may be better tolerated if given in 3 divided doses
 - Renal impairment, eGFR below 30 mL/min/1.73 m(2): Use is contraindicated 
@@ -2340,68 +2392,68 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" s="77">
-      <c r="A29" s="113" t="n"/>
-      <c r="B29" s="113" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" s="77">
-      <c r="A30" s="82" t="inlineStr">
+    <row r="29" ht="24" customHeight="1" s="81">
+      <c r="A29" s="120" t="n"/>
+      <c r="B29" s="120" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="81">
+      <c r="A30" s="86" t="inlineStr">
         <is>
           <t>Recommended as foundational therapy independent of baseline A1C or A1C target (ADA 2026 — unchanged).</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1" s="77">
-      <c r="A31" s="125" t="n"/>
-      <c r="B31" s="125" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1" s="77">
-      <c r="A32" s="114" t="inlineStr">
+    <row r="31" ht="24" customHeight="1" s="81">
+      <c r="A31" s="132" t="n"/>
+      <c r="B31" s="132" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="81">
+      <c r="A32" s="121" t="inlineStr">
         <is>
           <t>DRUG CLASS REFERENCE</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="77">
-      <c r="A33" s="126" t="inlineStr">
+    <row r="33" ht="15.75" customHeight="1" s="81">
+      <c r="A33" s="133" t="inlineStr">
         <is>
           <t>SGLT-2 Inhibitors</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1" s="77">
-      <c r="A34" s="112" t="inlineStr">
+    <row r="34" ht="30" customHeight="1" s="81">
+      <c r="A34" s="119" t="inlineStr">
         <is>
           <t>CVD Benefit (FDA approved)</t>
         </is>
       </c>
-      <c r="B34" s="111" t="inlineStr">
+      <c r="B34" s="118" t="inlineStr">
         <is>
           <t>- canagliflozin (Invokana)
 - empagliflozin (Jardiance)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="77">
-      <c r="A35" s="112" t="inlineStr">
+    <row r="35" ht="30" customHeight="1" s="81">
+      <c r="A35" s="119" t="inlineStr">
         <is>
           <t>HF Benefit (FDA approved)</t>
         </is>
       </c>
-      <c r="B35" s="111" t="inlineStr">
+      <c r="B35" s="118" t="inlineStr">
         <is>
           <t>- dapagliflozin (Farxiga)
 - empagliflozin (Jardiance)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="45" customHeight="1" s="77">
-      <c r="A36" s="112" t="inlineStr">
+    <row r="36" ht="45" customHeight="1" s="81">
+      <c r="A36" s="119" t="inlineStr">
         <is>
           <t>Renal benefit (FDA approved)</t>
         </is>
       </c>
-      <c r="B36" s="111" t="inlineStr">
+      <c r="B36" s="118" t="inlineStr">
         <is>
           <t>- canagliflozin (Invokana)
 - dapagliflozin (Farxiga)
@@ -2409,13 +2461,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1" s="77">
-      <c r="A37" s="112" t="inlineStr">
+    <row r="37" ht="60" customHeight="1" s="81">
+      <c r="A37" s="119" t="inlineStr">
         <is>
           <t>Dosing</t>
         </is>
       </c>
-      <c r="B37" s="111" t="inlineStr">
+      <c r="B37" s="118" t="inlineStr">
         <is>
           <t>- canagliflozin (Invokana) - Start 100 mg PO daily; max 300 mg daily
 - dapagliflozin (Farxiga) - Start 5 mg PO daily; max 10 mg daily
@@ -2423,13 +2475,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1" s="77">
-      <c r="A38" s="112" t="inlineStr">
+    <row r="38" ht="60" customHeight="1" s="81">
+      <c r="A38" s="119" t="inlineStr">
         <is>
           <t>eGFR cutoffs (glycemic indication)</t>
         </is>
       </c>
-      <c r="B38" s="111" t="inlineStr">
+      <c r="B38" s="118" t="inlineStr">
         <is>
           <t>- canagliflozin (Invokana): eGFR 30-50: max dose 100 mg once daily; eGFR &lt;30 or HD: Not recommended
 - dapagliflozin (Farxiga): eGFR &lt; 60: Contraindicated
@@ -2437,32 +2489,32 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="45" customHeight="1" s="77">
-      <c r="A39" s="118" t="inlineStr">
+    <row r="39" ht="45" customHeight="1" s="81">
+      <c r="A39" s="125" t="inlineStr">
         <is>
           <t>Cardiorenal combination (ADA 2026)</t>
         </is>
       </c>
-      <c r="B39" s="119" t="inlineStr">
+      <c r="B39" s="126" t="inlineStr">
         <is>
           <t>In T2DM with albuminuria (UACR ≥ 100 mg/g) and eGFR 30-90, consider combining an SGLT2i + finerenone (nonsteroidal MRA) + maximally tolerated ACEi/ARB for cardiorenal risk reduction.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="77">
-      <c r="A40" s="126" t="inlineStr">
+    <row r="40" ht="15.75" customHeight="1" s="81">
+      <c r="A40" s="133" t="inlineStr">
         <is>
           <t>GLP-1 RAs / GIP-GLP-1 RA</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="49.5" customHeight="1" s="77">
-      <c r="A41" s="112" t="inlineStr">
+    <row r="41" ht="49.5" customHeight="1" s="81">
+      <c r="A41" s="119" t="inlineStr">
         <is>
           <t>CVD Benefit (FDA approved)</t>
         </is>
       </c>
-      <c r="B41" s="111" t="inlineStr">
+      <c r="B41" s="118" t="inlineStr">
         <is>
           <t>- dulaglutide (Trulicity)
 - liraglutide (Victoza)
@@ -2470,37 +2522,37 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1" s="77">
-      <c r="A42" s="118" t="inlineStr">
+    <row r="42" ht="60" customHeight="1" s="81">
+      <c r="A42" s="125" t="inlineStr">
         <is>
           <t>HF Benefit</t>
         </is>
       </c>
-      <c r="B42" s="119" t="inlineStr">
+      <c r="B42" s="126" t="inlineStr">
         <is>
           <t>Neutral by FDA CV-outcome labeling for dulaglutide/liraglutide/semaglutide. GIP/GLP-1 RA (tirzepatide) shows benefit in HFpEF per the SUMMIT trial and is supported for HFpEF per ADA 2026 Standards of Care — this is guideline-based, not an FDA cardiovascular-outcome label.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="45" customHeight="1" s="77">
-      <c r="A43" s="118" t="inlineStr">
+    <row r="43" ht="45" customHeight="1" s="81">
+      <c r="A43" s="125" t="inlineStr">
         <is>
           <t>Renal Benefit</t>
         </is>
       </c>
-      <c r="B43" s="119" t="inlineStr">
+      <c r="B43" s="126" t="inlineStr">
         <is>
           <t>Not FDA-approved as a dedicated renal-outcome indication for this class. ADA 2026 now supports GLP-1 RA / GIP-GLP-1 RA use in T2DM with CKD as part of individualized cardiorenal care.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="99.75" customHeight="1" s="77">
-      <c r="A44" s="112" t="inlineStr">
+    <row r="44" ht="99.75" customHeight="1" s="81">
+      <c r="A44" s="119" t="inlineStr">
         <is>
           <t>Dosing</t>
         </is>
       </c>
-      <c r="B44" s="111" t="inlineStr">
+      <c r="B44" s="118" t="inlineStr">
         <is>
           <t>- dulaglutide (Trulicity) - Start 0.75 mg SQ once weekly; max to 1.5 mg SQ weekly
 - liraglutide (Victoza) - Start 0.6 mg SQ once daily for 1 week, then increase 1.2 mg once daily; then may increase to 1.8 mg daily
@@ -2509,73 +2561,73 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1" s="77">
-      <c r="A46" s="114" t="inlineStr">
+    <row r="46" ht="18" customHeight="1" s="81">
+      <c r="A46" s="121" t="inlineStr">
         <is>
           <t>ADDITIONAL INJECTABLE DOSING REFERENCE  (new — completes the drug list above)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="54.75" customHeight="1" s="77">
-      <c r="A47" s="118" t="inlineStr">
+    <row r="47" ht="54.75" customHeight="1" s="81">
+      <c r="A47" s="125" t="inlineStr">
         <is>
           <t>tirzepatide (Mounjaro)</t>
         </is>
       </c>
-      <c r="B47" s="119" t="inlineStr">
+      <c r="B47" s="126" t="inlineStr">
         <is>
           <t>Start 2.5 mg SQ once weekly x4 weeks (not for glycemic control); increase to 5 mg weekly; may increase in 2.5 mg increments after at least 4 weeks on current dose; max 15 mg weekly.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="54.75" customHeight="1" s="77">
-      <c r="A48" s="118" t="inlineStr">
+    <row r="48" ht="54.75" customHeight="1" s="81">
+      <c r="A48" s="125" t="inlineStr">
         <is>
           <t>exenatide (Byetta) / exenatide ER (Bydureon)</t>
         </is>
       </c>
-      <c r="B48" s="119" t="inlineStr">
+      <c r="B48" s="126" t="inlineStr">
         <is>
           <t>Byetta: start 5 mcg SQ twice daily within 60 minutes before meals, may increase to 10 mcg twice daily after 1 month.  Bydureon: 2 mg SQ once weekly, any time of day, with or without meals.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="54.75" customHeight="1" s="77">
-      <c r="A49" s="118" t="inlineStr">
+    <row r="49" ht="54.75" customHeight="1" s="81">
+      <c r="A49" s="125" t="inlineStr">
         <is>
           <t>pramlintide (SymlinPen)</t>
         </is>
       </c>
-      <c r="B49" s="119" t="inlineStr">
+      <c r="B49" s="126" t="inlineStr">
         <is>
           <t>Adjunct to mealtime insulin in T2DM: start 60 mcg SQ immediately before major meals; may increase to 120 mcg as tolerated. Reduce prandial insulin doses by 50% when initiating to reduce hypoglycemia risk.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1" s="77">
-      <c r="A51" s="114" t="inlineStr">
+    <row r="51" ht="18" customHeight="1" s="81">
+      <c r="A51" s="121" t="inlineStr">
         <is>
           <t>DEPRIORITIZED / FALLBACK AGENTS (ADA 2026)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="54.75" customHeight="1" s="77">
-      <c r="A52" s="127" t="inlineStr">
+    <row r="52" ht="54.75" customHeight="1" s="81">
+      <c r="A52" s="134" t="inlineStr">
         <is>
           <t>Sulfonylureas, meglitinides, and DPP-4 inhibitors remain fallback / cost-driven options — they lack cardiovascular, kidney, weight, or liver benefit relative to preferred agents. Use sulfonylureas and TZDs judiciously at the lowest effective dose given weight-gain and fracture risk, particularly in older adults.</t>
         </is>
       </c>
-      <c r="B52" s="128" t="n"/>
-    </row>
-    <row r="54" ht="45" customHeight="1" s="77">
-      <c r="A54" s="129" t="inlineStr">
+      <c r="B52" s="135" t="n"/>
+    </row>
+    <row r="54" ht="45" customHeight="1" s="81">
+      <c r="A54" s="136" t="inlineStr">
         <is>
           <t>Source: American Diabetes Association. Standards of Care in Diabetes—2026. Diabetes Care. 2026;49(Suppl 1), Section 9 (Pharmacologic Approaches to Glycemic Treatment). Injectable dosing verified against FDA prescribing information (DailyMed), accessed Aug 2026. Verify current oral semaglutide (Rybelsus) dosing/branding against the live FDA label before relying on this tool clinically — trade press reported a possible reformulation/brand transition not independently confirmed here.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="a80f"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="16">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A21:B21"/>
@@ -2619,363 +2671,363 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.00390625" defaultRowHeight="24" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="42" customWidth="1" style="110" min="1" max="1"/>
-    <col width="26" customWidth="1" style="110" min="2" max="2"/>
-    <col width="8" customWidth="1" style="110" min="3" max="3"/>
-    <col width="30" customWidth="1" style="110" min="4" max="4"/>
-    <col width="3" customWidth="1" style="110" min="5" max="16384"/>
+    <col width="42" customWidth="1" style="117" min="1" max="1"/>
+    <col width="26" customWidth="1" style="117" min="2" max="2"/>
+    <col width="8" customWidth="1" style="117" min="3" max="3"/>
+    <col width="30" customWidth="1" style="117" min="4" max="4"/>
+    <col width="3" customWidth="1" style="117" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="77">
-      <c r="A1" s="78" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="81">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>Diabetes Treatment Algorithm — Insulin Dosing</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="77">
-      <c r="A2" s="79" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="81">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>Select or Evaluate Initial Insulin Dose  |  Red = enter data  |  Blue = calculated  |  Green = new for ADA 2026</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="77">
-      <c r="A3" s="130" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="81">
+      <c r="A3" s="137" t="inlineStr">
         <is>
           <t>Disclaimer: use of this tool does not replace clinical judgment.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="77">
-      <c r="A5" s="114" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="81">
+      <c r="A5" s="121" t="inlineStr">
         <is>
           <t>Select Insulin Dosing Regimen — Initial</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="77">
-      <c r="A6" s="131" t="inlineStr">
+    <row r="6" ht="15.75" customHeight="1" s="81">
+      <c r="A6" s="138" t="inlineStr">
         <is>
           <t>Initiating Insulin in Type 1 Diabetes</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="77">
-      <c r="A7" s="112" t="inlineStr">
+    <row r="7" ht="15.75" customHeight="1" s="81">
+      <c r="A7" s="119" t="inlineStr">
         <is>
           <t>Insulin TDD</t>
         </is>
       </c>
-      <c r="B7" s="111" t="inlineStr">
+      <c r="B7" s="118" t="inlineStr">
         <is>
           <t>0.4-1.0 units/kg/day</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1" s="77">
-      <c r="B8" s="122">
+    <row r="8" ht="19.5" customHeight="1" s="81">
+      <c r="B8" s="129">
         <f>CONCATENATE(('Patient Information'!B7*0.4)," - ",('Patient Information'!B7*1)," units q daily")</f>
         <v/>
       </c>
-      <c r="C8" s="132" t="n"/>
-      <c r="D8" s="133" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" s="77">
-      <c r="A9" s="134" t="inlineStr">
+      <c r="C8" s="139" t="n"/>
+      <c r="D8" s="140" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="81">
+      <c r="A9" s="141" t="inlineStr">
         <is>
           <t>Basal-Bolus Strategy</t>
         </is>
       </c>
-      <c r="B9" s="135" t="n"/>
-      <c r="C9" s="135" t="n"/>
-      <c r="D9" s="135" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="77">
-      <c r="A10" s="136" t="inlineStr">
+      <c r="B9" s="142" t="n"/>
+      <c r="C9" s="142" t="n"/>
+      <c r="D9" s="142" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="81">
+      <c r="A10" s="143" t="inlineStr">
         <is>
           <t>If using Long-Acting + Rapid-Acting insulin (50/50)</t>
         </is>
       </c>
-      <c r="B10" s="122">
+      <c r="B10" s="129">
         <f>IF(OR(ISBLANK('Patient Information'!B7)), "", CONCATENATE(ROUND(0.5 * ('Patient Information'!B7 * 0.4), 0), " - ", ROUND((0.5 * 'Patient Information'!B7 * 1), 0), " units of basal q daily"))</f>
         <v/>
       </c>
-      <c r="C10" s="137" t="inlineStr">
+      <c r="C10" s="144" t="inlineStr">
         <is>
           <t>PLUS</t>
         </is>
       </c>
-      <c r="D10" s="122">
+      <c r="D10" s="129">
         <f>IF(ISBLANK('Patient Information'!B7), "", CONCATENATE(ROUND((0.5 * ('Patient Information'!B7 * 0.4)) / 3, 0), " - ", ROUND(((0.5 * 'Patient Information'!B7 * 1) / 3), 0), " units of bolus TID with meals"))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="77">
-      <c r="A11" s="136" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="81">
+      <c r="A11" s="143" t="inlineStr">
         <is>
           <t>If using NPH and regular insulin (2/3 , 1/3)</t>
         </is>
       </c>
-      <c r="B11" s="122">
+      <c r="B11" s="129">
         <f>IF(ISBLANK('Patient Information'!B7), "", CONCATENATE(ROUND(0.667 * ('Patient Information'!B7 * 0.4), 0), " - ", ROUND(0.667 * ('Patient Information'!B7 * 1), 0), " units of NPH BID"))</f>
         <v/>
       </c>
-      <c r="C11" s="137" t="inlineStr">
+      <c r="C11" s="144" t="inlineStr">
         <is>
           <t>PLUS</t>
         </is>
       </c>
-      <c r="D11" s="122">
+      <c r="D11" s="129">
         <f>IF(ISBLANK('Patient Information'!B7), "", CONCATENATE(ROUND(0.334 * ('Patient Information'!B7 * 0.4), 0), " - ", ROUND(0.334 * ('Patient Information'!B7 * 1), 0), " units of regular BID with meals"))</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="77">
-      <c r="A12" s="136" t="inlineStr">
+    <row r="12" ht="30" customHeight="1" s="81">
+      <c r="A12" s="143" t="inlineStr">
         <is>
           <t>if using insulin 70/30  (0.5 units/kg/day -- &gt; 2/3 AM +  1/3 PM)</t>
         </is>
       </c>
-      <c r="B12" s="122">
+      <c r="B12" s="129">
         <f>IF(ISBLANK('Patient Information'!B7), "", CONCATENATE(ROUND(('Patient Information'!B7 * 0.5) * 0.667, 0), " units of 70/30 AM + ", ROUND(('Patient Information'!B7 * 0.5) * 0.334, 0), " units of 70/30 PM with meals"))</f>
         <v/>
       </c>
-      <c r="C12" s="132" t="n"/>
-      <c r="D12" s="133" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" s="77">
-      <c r="A13" s="138" t="inlineStr">
+      <c r="C12" s="139" t="n"/>
+      <c r="D12" s="140" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="81">
+      <c r="A13" s="145" t="inlineStr">
         <is>
           <t>Initiating Insulin in Type 2 Diabetes</t>
         </is>
       </c>
-      <c r="B13" s="139" t="n"/>
-      <c r="C13" s="139" t="n"/>
-      <c r="D13" s="139" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="77">
-      <c r="A14" s="112" t="inlineStr">
+      <c r="B13" s="146" t="n"/>
+      <c r="C13" s="146" t="n"/>
+      <c r="D13" s="146" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="81">
+      <c r="A14" s="119" t="inlineStr">
         <is>
           <t>Basal Insulin Dose</t>
         </is>
       </c>
-      <c r="B14" s="111" t="inlineStr">
+      <c r="B14" s="118" t="inlineStr">
         <is>
           <t>Basal Insulin is initated at 10 units daily OR 0.1-0.2 units/kg/day</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="77">
-      <c r="B15" s="111" t="inlineStr">
+    <row r="15" ht="15.75" customHeight="1" s="81">
+      <c r="B15" s="118" t="inlineStr">
         <is>
           <t>10 units q daily</t>
         </is>
       </c>
-      <c r="C15" s="140" t="inlineStr">
+      <c r="C15" s="147" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D15" s="122">
+      <c r="D15" s="129">
         <f>IF(ISBLANK('Patient Information'!B7), "", CONCATENATE(('Patient Information'!B7*0.1)," - ",('Patient Information'!B7*0.2)," units q daily"))</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="7.5" customHeight="1" s="77">
-      <c r="A16" s="141" t="n"/>
-      <c r="B16" s="141" t="n"/>
-      <c r="C16" s="141" t="n"/>
-      <c r="D16" s="141" t="n"/>
-      <c r="E16" s="142" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" s="77">
-      <c r="A17" s="114" t="inlineStr">
+    <row r="16" ht="7.5" customHeight="1" s="81">
+      <c r="A16" s="148" t="n"/>
+      <c r="B16" s="148" t="n"/>
+      <c r="C16" s="148" t="n"/>
+      <c r="D16" s="148" t="n"/>
+      <c r="E16" s="149" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="81">
+      <c r="A17" s="121" t="inlineStr">
         <is>
           <t>Adjusting Insulin Regimen</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="77">
-      <c r="A18" s="143" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="81">
+      <c r="A18" s="150" t="inlineStr">
         <is>
           <t>Enter TDD of insulin</t>
         </is>
       </c>
-      <c r="B18" s="121" t="n"/>
-      <c r="C18" s="144" t="n"/>
-      <c r="D18" s="145" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="77">
-      <c r="A19" s="112" t="inlineStr">
+      <c r="B18" s="128" t="n"/>
+      <c r="C18" s="156" t="n"/>
+      <c r="D18" s="157" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="81">
+      <c r="A19" s="119" t="inlineStr">
         <is>
           <t>Adding bolus insulin in T2DM</t>
         </is>
       </c>
-      <c r="B19" s="111" t="inlineStr">
+      <c r="B19" s="118" t="inlineStr">
         <is>
           <t>If not at goal, bolus insulin is initiated at 4 units/day OR 10% of TDD</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="77">
-      <c r="B20" s="122" t="inlineStr">
+    <row r="20" ht="15.75" customHeight="1" s="81">
+      <c r="B20" s="129" t="inlineStr">
         <is>
           <t>4 units per day with largest meal</t>
         </is>
       </c>
-      <c r="C20" s="140" t="inlineStr">
+      <c r="C20" s="147" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="D20" s="122">
+      <c r="D20" s="129">
         <f>IF(ISBLANK(B18), "", CONCATENATE(ROUND(B18*0.1, 0), " units per day with largest meal"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="77">
-      <c r="A21" s="143" t="inlineStr">
+    <row r="21" ht="15.75" customHeight="1" s="81">
+      <c r="A21" s="150" t="inlineStr">
         <is>
           <t>Enter rapid or regular Insulin as bolus?</t>
         </is>
       </c>
-      <c r="B21" s="121" t="n"/>
-      <c r="C21" s="144" t="n"/>
-      <c r="D21" s="145" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1" s="77">
-      <c r="A22" s="112" t="inlineStr">
+      <c r="B21" s="128" t="n"/>
+      <c r="C21" s="156" t="n"/>
+      <c r="D21" s="157" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" s="81">
+      <c r="A22" s="119" t="inlineStr">
         <is>
           <t>Insulin sensitivity factor (rule of 1800 or 1500)</t>
         </is>
       </c>
-      <c r="B22" s="122">
+      <c r="B22" s="129">
         <f>IF(OR(ISBLANK(B21),ISBLANK(B18)),"",IF(B21="rapid",CONCATENATE(ROUND(1800/B18,0)," mg/dL lowered by 1 unit of rapid"),IF(B21="regular",CONCATENATE(ROUND(1500/B18,0)," mg/dL of glucose lowered by 1 unit of regular"),"")))</f>
         <v/>
       </c>
-      <c r="C22" s="132" t="n"/>
-      <c r="D22" s="133" t="n"/>
-    </row>
-    <row r="23" ht="30" customHeight="1" s="77">
-      <c r="A23" s="112" t="inlineStr">
+      <c r="C22" s="139" t="n"/>
+      <c r="D22" s="140" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" s="81">
+      <c r="A23" s="119" t="inlineStr">
         <is>
           <t>Insulin-to-carb ratio (rule of 500 or 450)</t>
         </is>
       </c>
-      <c r="B23" s="122">
+      <c r="B23" s="129">
         <f>IF(OR(ISBLANK(B21), ISBLANK(B18)), "", IF(B21="rapid", CONCATENATE(ROUND(500/B18, 0), " grams of carb covered by 1 unit of rapid"), IF(B21="regular", CONCATENATE(ROUND(450/B18, 0), " grams of carb covered by 1 unit of regular"), "")))</f>
         <v/>
       </c>
-      <c r="C23" s="132" t="n"/>
-      <c r="D23" s="133" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="77">
-      <c r="A24" s="112" t="inlineStr">
+      <c r="C23" s="139" t="n"/>
+      <c r="D23" s="140" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="81">
+      <c r="A24" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">Correction Dose </t>
         </is>
       </c>
-      <c r="B24" s="111" t="inlineStr">
+      <c r="B24" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">[Current BG - Target BG]/Correction Factor </t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="77">
-      <c r="A25" s="112" t="inlineStr">
+    <row r="25" ht="15.75" customHeight="1" s="81">
+      <c r="A25" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">Enter current BG </t>
         </is>
       </c>
-      <c r="B25" s="121" t="n"/>
-      <c r="C25" s="144" t="n"/>
-      <c r="D25" s="145" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" s="77">
-      <c r="A26" s="112" t="inlineStr">
+      <c r="B25" s="128" t="n"/>
+      <c r="C25" s="156" t="n"/>
+      <c r="D25" s="157" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="81">
+      <c r="A26" s="119" t="inlineStr">
         <is>
           <t>Enter target BG</t>
         </is>
       </c>
-      <c r="B26" s="121" t="n"/>
-      <c r="C26" s="144" t="n"/>
-      <c r="D26" s="145" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="77">
-      <c r="A27" s="112" t="inlineStr">
+      <c r="B26" s="128" t="n"/>
+      <c r="C26" s="156" t="n"/>
+      <c r="D26" s="157" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="81">
+      <c r="A27" s="119" t="inlineStr">
         <is>
           <t>Calculated Correction Dose</t>
         </is>
       </c>
-      <c r="B27" s="122">
+      <c r="B27" s="129">
         <f>IF(OR(ISBLANK(B21), ISBLANK(B25), ISBLANK(B26), ISBLANK(B18)), "", IF(B21="rapid", ROUND((B25-B26)/(1800/B18), 0) &amp; " units of rapid insulin", IF(B21="regular", ROUND((B25-B26)/(1500/B18), 0) &amp; " units of regular insulin", "")))</f>
         <v/>
       </c>
-      <c r="C27" s="132" t="n"/>
-      <c r="D27" s="133" t="n"/>
-    </row>
-    <row r="28" ht="7.5" customHeight="1" s="77">
-      <c r="A28" s="141" t="n"/>
-      <c r="B28" s="146" t="n"/>
-      <c r="C28" s="146" t="n"/>
-      <c r="D28" s="146" t="n"/>
-      <c r="E28" s="142" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" s="77">
-      <c r="A29" s="114" t="inlineStr">
+      <c r="C27" s="139" t="n"/>
+      <c r="D27" s="140" t="n"/>
+    </row>
+    <row r="28" ht="7.5" customHeight="1" s="81">
+      <c r="A28" s="148" t="n"/>
+      <c r="B28" s="153" t="n"/>
+      <c r="C28" s="153" t="n"/>
+      <c r="D28" s="153" t="n"/>
+      <c r="E28" s="149" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="81">
+      <c r="A29" s="121" t="inlineStr">
         <is>
           <t>Insulin Conversions</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1" s="77">
-      <c r="A30" s="147" t="inlineStr">
+    <row r="30" ht="24" customHeight="1" s="81">
+      <c r="A30" s="154" t="inlineStr">
         <is>
           <t>Basal insulin conversions</t>
         </is>
       </c>
-      <c r="B30" s="148" t="n"/>
-      <c r="C30" s="148" t="n"/>
-      <c r="D30" s="148" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" s="77">
-      <c r="A31" s="112" t="inlineStr">
+      <c r="B30" s="155" t="n"/>
+      <c r="C30" s="155" t="n"/>
+      <c r="D30" s="155" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="81">
+      <c r="A31" s="119" t="inlineStr">
         <is>
           <t>Enter current basal insulin</t>
         </is>
       </c>
-      <c r="B31" s="121" t="n"/>
-      <c r="C31" s="144" t="n"/>
-      <c r="D31" s="145" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" s="77">
-      <c r="A32" s="112" t="inlineStr">
+      <c r="B31" s="128" t="n"/>
+      <c r="C31" s="156" t="n"/>
+      <c r="D31" s="157" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="81">
+      <c r="A32" s="119" t="inlineStr">
         <is>
           <t>Enter current insulin dose</t>
         </is>
       </c>
-      <c r="B32" s="121" t="n"/>
-      <c r="C32" s="144" t="n"/>
-      <c r="D32" s="145" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" s="77">
-      <c r="A33" s="112" t="inlineStr">
+      <c r="B32" s="128" t="n"/>
+      <c r="C32" s="156" t="n"/>
+      <c r="D32" s="157" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="81">
+      <c r="A33" s="119" t="inlineStr">
         <is>
           <t>Enter desired basal insulin</t>
         </is>
       </c>
-      <c r="B33" s="121" t="n"/>
-      <c r="C33" s="144" t="n"/>
-      <c r="D33" s="145" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" s="77">
-      <c r="A34" s="112" t="inlineStr">
+      <c r="B33" s="128" t="n"/>
+      <c r="C33" s="156" t="n"/>
+      <c r="D33" s="157" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="81">
+      <c r="A34" s="119" t="inlineStr">
         <is>
           <t>Calculated desired insulin dose (TDD)</t>
         </is>
       </c>
-      <c r="B34" s="122">
+      <c r="B34" s="129">
         <f>IF(OR(ISBLANK(B31), ISBLANK(B32), ISBLANK(B33)), "",
    IF(AND(B31="NPH BID", NOT(OR(B33="NPH BID", B33="Insulin degludec (Tresiba)", B33="Insulin detemir (Levemir)"))), B32*0.8,
       IF(AND(NOT(OR(B31="NPH BID", B31="Insulin detemir (Levemir)", B31="Insulin degludec (Tresiba)")), OR(B33="NPH BID", B33="Insulin detemir (Levemir)", B33="Insulin degludec (Tresiba)")), B32/0.8,
@@ -2991,56 +3043,56 @@
 )</f>
         <v/>
       </c>
-      <c r="C34" s="132" t="n"/>
-      <c r="D34" s="133" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" s="77">
-      <c r="A35" s="147" t="inlineStr">
+      <c r="C34" s="139" t="n"/>
+      <c r="D34" s="140" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" s="81">
+      <c r="A35" s="154" t="inlineStr">
         <is>
           <t>Bolus insulin conversions</t>
         </is>
       </c>
-      <c r="B35" s="148" t="n"/>
-      <c r="C35" s="148" t="n"/>
-      <c r="D35" s="148" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" s="77">
-      <c r="A36" s="112" t="inlineStr">
+      <c r="B35" s="155" t="n"/>
+      <c r="C35" s="155" t="n"/>
+      <c r="D35" s="155" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="81">
+      <c r="A36" s="119" t="inlineStr">
         <is>
           <t>Enter current bolus insulin</t>
         </is>
       </c>
-      <c r="B36" s="121" t="n"/>
-      <c r="C36" s="144" t="n"/>
-      <c r="D36" s="145" t="n"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" s="77">
-      <c r="A37" s="112" t="inlineStr">
+      <c r="B36" s="128" t="n"/>
+      <c r="C36" s="156" t="n"/>
+      <c r="D36" s="157" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="81">
+      <c r="A37" s="119" t="inlineStr">
         <is>
           <t>Enter current insulin dose</t>
         </is>
       </c>
-      <c r="B37" s="121" t="n"/>
-      <c r="C37" s="144" t="n"/>
-      <c r="D37" s="145" t="n"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" s="77">
-      <c r="A38" s="112" t="inlineStr">
+      <c r="B37" s="128" t="n"/>
+      <c r="C37" s="156" t="n"/>
+      <c r="D37" s="157" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="81">
+      <c r="A38" s="119" t="inlineStr">
         <is>
           <t>Enter desired bolus  insulin</t>
         </is>
       </c>
-      <c r="B38" s="121" t="n"/>
-      <c r="C38" s="144" t="n"/>
-      <c r="D38" s="145" t="n"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" s="77">
-      <c r="A39" s="112" t="inlineStr">
+      <c r="B38" s="128" t="n"/>
+      <c r="C38" s="156" t="n"/>
+      <c r="D38" s="157" t="n"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="81">
+      <c r="A39" s="119" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculated desired insulin dose </t>
         </is>
       </c>
-      <c r="B39" s="122">
+      <c r="B39" s="129">
         <f>IF(OR(ISBLANK(B36), ISBLANK(B37), ISBLANK(B38)), "",
    IF(AND(B36="Regular (R)", OR(B38="Insulin aspart (Novolog)", B38="Insulin lispro (Humalog)", B38="Insulin glulisine (Apidra)")), B37*0.8,
       IF(AND(OR(B36="Insulin aspart (Novolog)", B36="Insulin lispro (Humalog)", B36="Insulin glulisine (Apidra)"), B38="Regular (R)"), B37/0.8, B37)
@@ -3048,170 +3100,170 @@
 )</f>
         <v/>
       </c>
-      <c r="C39" s="132" t="n"/>
-      <c r="D39" s="133" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1" s="77">
-      <c r="A40" s="147" t="inlineStr">
+      <c r="C39" s="139" t="n"/>
+      <c r="D39" s="140" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1" s="81">
+      <c r="A40" s="154" t="inlineStr">
         <is>
           <t>Mixed insulin conversions</t>
         </is>
       </c>
-      <c r="B40" s="148" t="n"/>
-      <c r="C40" s="148" t="n"/>
-      <c r="D40" s="148" t="n"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" s="77">
-      <c r="A41" s="112" t="inlineStr">
+      <c r="B40" s="155" t="n"/>
+      <c r="C40" s="155" t="n"/>
+      <c r="D40" s="155" t="n"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="81">
+      <c r="A41" s="119" t="inlineStr">
         <is>
           <t>Enter current mixed insulin</t>
         </is>
       </c>
-      <c r="B41" s="121" t="n"/>
-      <c r="C41" s="144" t="n"/>
-      <c r="D41" s="145" t="n"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" s="77">
-      <c r="A42" s="112" t="inlineStr">
+      <c r="B41" s="128" t="n"/>
+      <c r="C41" s="156" t="n"/>
+      <c r="D41" s="157" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="81">
+      <c r="A42" s="119" t="inlineStr">
         <is>
           <t>Enter current insulin dose</t>
         </is>
       </c>
-      <c r="B42" s="121" t="n"/>
-      <c r="C42" s="144" t="n"/>
-      <c r="D42" s="145" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" s="77">
-      <c r="A43" s="112" t="inlineStr">
+      <c r="B42" s="128" t="n"/>
+      <c r="C42" s="156" t="n"/>
+      <c r="D42" s="157" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="81">
+      <c r="A43" s="119" t="inlineStr">
         <is>
           <t>Enter desired mixed insulin</t>
         </is>
       </c>
-      <c r="B43" s="121" t="n"/>
-      <c r="C43" s="144" t="n"/>
-      <c r="D43" s="145" t="n"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" s="77">
-      <c r="A44" s="112" t="inlineStr">
+      <c r="B43" s="128" t="n"/>
+      <c r="C43" s="156" t="n"/>
+      <c r="D43" s="157" t="n"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="81">
+      <c r="A44" s="119" t="inlineStr">
         <is>
           <t>Calculated desired insulin dose (TDD)</t>
         </is>
       </c>
-      <c r="B44" s="122">
+      <c r="B44" s="129">
         <f>IF(OR(ISBLANK(B41), ISBLANK(B42), ISBLANK(B43)), "", IF(AND(B41="NPH BID", NOT(OR(B43="Insulin degludec (Tresiba)", B43="Insulin detemir (Levemir)"))), B42*0.8, IF(AND(B41="Insulin glargine (Toujeo)", NOT(B43="Insulin degludec (Tresiba)")), B42*0.8, B42)))</f>
         <v/>
       </c>
-      <c r="C44" s="132" t="n"/>
-      <c r="D44" s="133" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1" s="77">
-      <c r="A46" s="149" t="inlineStr">
+      <c r="C44" s="139" t="n"/>
+      <c r="D44" s="140" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="81">
+      <c r="A46" s="158" t="inlineStr">
         <is>
           <t>ONCE-WEEKLY BASAL INSULIN — INSULIN ICODEC (AWIQLI)  —  new, FDA-approved March 2026</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="45" customHeight="1" s="77">
-      <c r="A47" s="118" t="inlineStr">
+    <row r="47" ht="45" customHeight="1" s="81">
+      <c r="A47" s="125" t="inlineStr">
         <is>
           <t>Formulation</t>
         </is>
       </c>
-      <c r="B47" s="119" t="inlineStr">
+      <c r="B47" s="126" t="inlineStr">
         <is>
           <t>U-700 (700 units/mL) — about 7x more concentrated than standard U-100 basal insulins. Use only the Awiqli FlexTouch pen; never withdraw into a syringe. Do not mix or dilute with any other insulin.</t>
         </is>
       </c>
-      <c r="C47" s="150" t="n"/>
-      <c r="D47" s="120" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1" s="77">
-      <c r="A48" s="118" t="inlineStr">
+      <c r="C47" s="159" t="n"/>
+      <c r="D47" s="127" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1" s="81">
+      <c r="A48" s="125" t="inlineStr">
         <is>
           <t>Insulin-naive starting dose</t>
         </is>
       </c>
-      <c r="B48" s="119" t="inlineStr">
+      <c r="B48" s="126" t="inlineStr">
         <is>
           <t>70 units SQ once weekly, same day each week.</t>
         </is>
       </c>
-      <c r="C48" s="150" t="n"/>
-      <c r="D48" s="120" t="n"/>
-    </row>
-    <row r="49" ht="30" customHeight="1" s="77">
-      <c r="A49" s="118" t="inlineStr">
+      <c r="C48" s="159" t="n"/>
+      <c r="D48" s="127" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1" s="81">
+      <c r="A49" s="125" t="inlineStr">
         <is>
           <t>Enter current total daily dose of basal insulin (units) — for patients switching from daily basal</t>
         </is>
       </c>
-      <c r="B49" s="121" t="n"/>
-      <c r="C49" s="144" t="n"/>
-      <c r="D49" s="145" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1" s="77">
-      <c r="A50" s="118" t="inlineStr">
+      <c r="B49" s="128" t="n"/>
+      <c r="C49" s="156" t="n"/>
+      <c r="D49" s="157" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1" s="81">
+      <c r="A50" s="125" t="inlineStr">
         <is>
           <t>Week 1 dose (one-time starting dose)</t>
         </is>
       </c>
-      <c r="B50" s="118">
+      <c r="B50" s="125">
         <f>IF(ISBLANK(B49),"",CONCATENATE(ROUND((1.5*B49*7)/10,0)*10," units (one-time starting dose)"))</f>
         <v/>
       </c>
-      <c r="C50" s="150" t="n"/>
-      <c r="D50" s="120" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1" s="77">
-      <c r="A51" s="118" t="inlineStr">
+      <c r="C50" s="159" t="n"/>
+      <c r="D50" s="127" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="81">
+      <c r="A51" s="125" t="inlineStr">
         <is>
           <t>Week 2 dose</t>
         </is>
       </c>
-      <c r="B51" s="118">
+      <c r="B51" s="125">
         <f>IF(ISBLANK(B49),"",CONCATENATE(ROUND((B49*7)/10,0)*10," units"))</f>
         <v/>
       </c>
-      <c r="C51" s="150" t="n"/>
-      <c r="D51" s="120" t="n"/>
-    </row>
-    <row r="52" ht="30" customHeight="1" s="77">
-      <c r="A52" s="118" t="inlineStr">
+      <c r="C51" s="159" t="n"/>
+      <c r="D51" s="127" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1" s="81">
+      <c r="A52" s="125" t="inlineStr">
         <is>
           <t>Week 3 and beyond</t>
         </is>
       </c>
-      <c r="B52" s="119" t="inlineStr">
+      <c r="B52" s="126" t="inlineStr">
         <is>
           <t>Titrate from the prior weekly dose based on metabolic needs, blood glucose monitoring, and glycemic goals.</t>
         </is>
       </c>
-      <c r="C52" s="150" t="n"/>
-      <c r="D52" s="120" t="n"/>
-    </row>
-    <row r="53" ht="69.75" customHeight="1" s="77">
-      <c r="A53" s="118" t="inlineStr">
+      <c r="C52" s="159" t="n"/>
+      <c r="D52" s="127" t="n"/>
+    </row>
+    <row r="53" ht="69.75" customHeight="1" s="81">
+      <c r="A53" s="125" t="inlineStr">
         <is>
           <t>Administration notes</t>
         </is>
       </c>
-      <c r="B53" s="119" t="inlineStr">
+      <c r="B53" s="126" t="inlineStr">
         <is>
           <t>Give the first Awiqli dose the day after the last daily basal dose. Doses in 10-unit increments; max 700 units per single injection (doses above 700 units require split injections). If a dose is missed, take within 4 days of the missed dose; if more than 4 days have passed, skip and resume on the next scheduled day.</t>
         </is>
       </c>
-      <c r="C53" s="150" t="n"/>
-      <c r="D53" s="120" t="n"/>
-    </row>
-    <row r="55" ht="30" customHeight="1" s="77">
-      <c r="A55" s="129" t="inlineStr">
+      <c r="C53" s="159" t="n"/>
+      <c r="D53" s="127" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1" s="81">
+      <c r="A55" s="136" t="inlineStr">
         <is>
           <t>Source: Awiqli (insulin icodec-abae) FDA Prescribing Information, DailyMed, revised 3/2026, accessed Aug 2026. All other insulin initiation/titration figures on this tab are carried over from prior Standards of Care — no ADA-specific numeric changes were identified for 2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="a80f"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="43">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
@@ -3290,646 +3342,646 @@
   <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.66796875" defaultRowHeight="15.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="20" customWidth="1" style="76" min="1" max="1"/>
-    <col width="9" customWidth="1" style="76" min="2" max="7"/>
-    <col width="16" customWidth="1" style="76" min="8" max="8"/>
-    <col width="3" customWidth="1" style="76" min="9" max="10"/>
-    <col width="26" customWidth="1" style="76" min="11" max="11"/>
-    <col width="12" customWidth="1" style="76" min="12" max="12"/>
-    <col width="16" customWidth="1" style="76" min="13" max="13"/>
+    <col width="20" customWidth="1" style="80" min="1" max="1"/>
+    <col width="9" customWidth="1" style="80" min="2" max="7"/>
+    <col width="16" customWidth="1" style="80" min="8" max="8"/>
+    <col width="3" customWidth="1" style="80" min="9" max="10"/>
+    <col width="26" customWidth="1" style="80" min="11" max="11"/>
+    <col width="12" customWidth="1" style="80" min="12" max="12"/>
+    <col width="16" customWidth="1" style="80" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="77">
-      <c r="A1" s="78" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="81">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>Diabetes Treatment Algorithm — SMBG Averages</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="77">
-      <c r="A2" s="79" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="81">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>SMBG Averages  |  Red = enter data  |  Blue = calculated  |  Green = new for ADA 2026</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="77">
-      <c r="A3" s="130" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="81">
+      <c r="A3" s="137" t="inlineStr">
         <is>
           <t>Disclaimer: use of this tool does not replace clinical judgment.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="77">
-      <c r="A4" s="151" t="n"/>
-      <c r="B4" s="152" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="81">
+      <c r="A4" s="160" t="n"/>
+      <c r="B4" s="161" t="inlineStr">
         <is>
           <t xml:space="preserve">Enter SMBG values </t>
         </is>
       </c>
-      <c r="C4" s="153" t="n"/>
-      <c r="D4" s="153" t="n"/>
-      <c r="E4" s="153" t="n"/>
-      <c r="F4" s="153" t="n"/>
-      <c r="G4" s="154" t="n"/>
-      <c r="H4" s="152" t="inlineStr">
+      <c r="C4" s="162" t="n"/>
+      <c r="D4" s="162" t="n"/>
+      <c r="E4" s="162" t="n"/>
+      <c r="F4" s="162" t="n"/>
+      <c r="G4" s="163" t="n"/>
+      <c r="H4" s="161" t="inlineStr">
         <is>
           <t xml:space="preserve">Running average </t>
         </is>
       </c>
-      <c r="K4" s="152" t="inlineStr">
+      <c r="K4" s="161" t="inlineStr">
         <is>
           <t>ADA Blood Sugar Goals</t>
         </is>
       </c>
-      <c r="L4" s="154" t="n"/>
-      <c r="M4" s="151" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="77">
-      <c r="A5" s="155" t="inlineStr">
+      <c r="L4" s="163" t="n"/>
+      <c r="M4" s="160" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="81">
+      <c r="A5" s="164" t="inlineStr">
         <is>
           <t>Before Breakfast</t>
         </is>
       </c>
-      <c r="B5" s="156" t="n"/>
-      <c r="C5" s="156" t="n"/>
-      <c r="D5" s="156" t="n"/>
-      <c r="E5" s="156" t="n"/>
-      <c r="F5" s="156" t="n"/>
-      <c r="G5" s="156" t="n"/>
-      <c r="H5" s="100">
+      <c r="B5" s="165" t="n"/>
+      <c r="C5" s="165" t="n"/>
+      <c r="D5" s="165" t="n"/>
+      <c r="E5" s="165" t="n"/>
+      <c r="F5" s="165" t="n"/>
+      <c r="G5" s="165" t="n"/>
+      <c r="H5" s="107">
         <f>IF(COUNT(B5:G9) &gt; 0, ROUND(AVERAGE(B5:G9), 1), "")</f>
         <v/>
       </c>
-      <c r="K5" s="157" t="inlineStr">
+      <c r="K5" s="166" t="inlineStr">
         <is>
           <t>A1c</t>
         </is>
       </c>
-      <c r="L5" s="158" t="inlineStr">
+      <c r="L5" s="167" t="inlineStr">
         <is>
           <t>&lt;7%</t>
         </is>
       </c>
-      <c r="M5" s="151" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="77">
-      <c r="A6" s="159" t="n"/>
-      <c r="B6" s="156" t="n"/>
-      <c r="C6" s="156" t="n"/>
-      <c r="D6" s="156" t="n"/>
-      <c r="E6" s="156" t="n"/>
-      <c r="F6" s="156" t="n"/>
-      <c r="G6" s="156" t="n"/>
-      <c r="H6" s="160" t="n"/>
-      <c r="K6" s="157" t="inlineStr">
+      <c r="M5" s="160" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="81">
+      <c r="A6" s="168" t="n"/>
+      <c r="B6" s="165" t="n"/>
+      <c r="C6" s="165" t="n"/>
+      <c r="D6" s="165" t="n"/>
+      <c r="E6" s="165" t="n"/>
+      <c r="F6" s="165" t="n"/>
+      <c r="G6" s="165" t="n"/>
+      <c r="H6" s="169" t="n"/>
+      <c r="K6" s="166" t="inlineStr">
         <is>
           <t>Fasting</t>
         </is>
       </c>
-      <c r="L6" s="158" t="inlineStr">
+      <c r="L6" s="167" t="inlineStr">
         <is>
           <t>80-130</t>
         </is>
       </c>
-      <c r="M6" s="151" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="77">
-      <c r="A7" s="159" t="n"/>
-      <c r="B7" s="156" t="n"/>
-      <c r="C7" s="156" t="n"/>
-      <c r="D7" s="156" t="n"/>
-      <c r="E7" s="156" t="n"/>
-      <c r="F7" s="156" t="n"/>
-      <c r="G7" s="156" t="n"/>
-      <c r="H7" s="160" t="n"/>
-      <c r="K7" s="157" t="inlineStr">
+      <c r="M6" s="160" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="81">
+      <c r="A7" s="168" t="n"/>
+      <c r="B7" s="165" t="n"/>
+      <c r="C7" s="165" t="n"/>
+      <c r="D7" s="165" t="n"/>
+      <c r="E7" s="165" t="n"/>
+      <c r="F7" s="165" t="n"/>
+      <c r="G7" s="165" t="n"/>
+      <c r="H7" s="169" t="n"/>
+      <c r="K7" s="166" t="inlineStr">
         <is>
           <t>2 hours post-prandial</t>
         </is>
       </c>
-      <c r="L7" s="158" t="inlineStr">
+      <c r="L7" s="167" t="inlineStr">
         <is>
           <t>&lt; 180</t>
         </is>
       </c>
-      <c r="M7" s="151" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="77">
-      <c r="A8" s="159" t="n"/>
-      <c r="B8" s="156" t="n"/>
-      <c r="C8" s="156" t="n"/>
-      <c r="D8" s="156" t="n"/>
-      <c r="E8" s="156" t="n"/>
-      <c r="F8" s="156" t="n"/>
-      <c r="G8" s="156" t="n"/>
-      <c r="H8" s="160" t="n"/>
-      <c r="K8" s="157" t="inlineStr">
+      <c r="M7" s="160" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="81">
+      <c r="A8" s="168" t="n"/>
+      <c r="B8" s="165" t="n"/>
+      <c r="C8" s="165" t="n"/>
+      <c r="D8" s="165" t="n"/>
+      <c r="E8" s="165" t="n"/>
+      <c r="F8" s="165" t="n"/>
+      <c r="G8" s="165" t="n"/>
+      <c r="H8" s="169" t="n"/>
+      <c r="K8" s="166" t="inlineStr">
         <is>
           <t>Hypoglycemia</t>
         </is>
       </c>
-      <c r="L8" s="158" t="inlineStr">
+      <c r="L8" s="167" t="inlineStr">
         <is>
           <t>&lt;70</t>
         </is>
       </c>
-      <c r="M8" s="151" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="77">
-      <c r="A9" s="161" t="n"/>
-      <c r="B9" s="156" t="n"/>
-      <c r="C9" s="156" t="n"/>
-      <c r="D9" s="156" t="n"/>
-      <c r="E9" s="156" t="n"/>
-      <c r="F9" s="156" t="n"/>
-      <c r="G9" s="156" t="n"/>
-      <c r="H9" s="162" t="n"/>
-      <c r="K9" s="151" t="n"/>
-      <c r="L9" s="151" t="n"/>
-      <c r="M9" s="151" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="77">
-      <c r="A10" s="155" t="inlineStr">
+      <c r="M8" s="160" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="81">
+      <c r="A9" s="170" t="n"/>
+      <c r="B9" s="165" t="n"/>
+      <c r="C9" s="165" t="n"/>
+      <c r="D9" s="165" t="n"/>
+      <c r="E9" s="165" t="n"/>
+      <c r="F9" s="165" t="n"/>
+      <c r="G9" s="165" t="n"/>
+      <c r="H9" s="171" t="n"/>
+      <c r="K9" s="160" t="n"/>
+      <c r="L9" s="160" t="n"/>
+      <c r="M9" s="160" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="81">
+      <c r="A10" s="164" t="inlineStr">
         <is>
           <t>After Breakfast</t>
         </is>
       </c>
-      <c r="B10" s="156" t="n"/>
-      <c r="C10" s="156" t="n"/>
-      <c r="D10" s="156" t="n"/>
-      <c r="E10" s="156" t="n"/>
-      <c r="F10" s="156" t="n"/>
-      <c r="G10" s="156" t="n"/>
-      <c r="H10" s="100">
+      <c r="B10" s="165" t="n"/>
+      <c r="C10" s="165" t="n"/>
+      <c r="D10" s="165" t="n"/>
+      <c r="E10" s="165" t="n"/>
+      <c r="F10" s="165" t="n"/>
+      <c r="G10" s="165" t="n"/>
+      <c r="H10" s="107">
         <f>IF(COUNT(B10:G14) &gt; 0, ROUND(AVERAGE(B10:G14), 1), "")</f>
         <v/>
       </c>
-      <c r="K10" s="163" t="inlineStr">
+      <c r="K10" s="172" t="inlineStr">
         <is>
           <t>Hypoglycemic SMBG &lt; 70  will change cell red</t>
         </is>
       </c>
-      <c r="L10" s="154" t="n"/>
-      <c r="M10" s="151" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="77">
-      <c r="A11" s="159" t="n"/>
-      <c r="B11" s="156" t="n"/>
-      <c r="C11" s="156" t="n"/>
-      <c r="D11" s="156" t="n"/>
-      <c r="E11" s="156" t="n"/>
-      <c r="F11" s="156" t="n"/>
-      <c r="G11" s="156" t="n"/>
-      <c r="H11" s="160" t="n"/>
-      <c r="K11" s="163" t="inlineStr">
+      <c r="L10" s="163" t="n"/>
+      <c r="M10" s="160" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="81">
+      <c r="A11" s="168" t="n"/>
+      <c r="B11" s="165" t="n"/>
+      <c r="C11" s="165" t="n"/>
+      <c r="D11" s="165" t="n"/>
+      <c r="E11" s="165" t="n"/>
+      <c r="F11" s="165" t="n"/>
+      <c r="G11" s="165" t="n"/>
+      <c r="H11" s="169" t="n"/>
+      <c r="K11" s="172" t="inlineStr">
         <is>
           <t>SMBG &gt; 180 will change cell purple</t>
         </is>
       </c>
-      <c r="L11" s="154" t="n"/>
-      <c r="M11" s="151" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="77">
-      <c r="A12" s="159" t="n"/>
-      <c r="B12" s="156" t="n"/>
-      <c r="C12" s="156" t="n"/>
-      <c r="D12" s="156" t="n"/>
-      <c r="E12" s="156" t="n"/>
-      <c r="F12" s="156" t="n"/>
-      <c r="G12" s="156" t="n"/>
-      <c r="H12" s="160" t="n"/>
-      <c r="K12" s="151" t="n"/>
-      <c r="L12" s="151" t="n"/>
-      <c r="M12" s="151" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="77">
-      <c r="A13" s="159" t="n"/>
-      <c r="B13" s="156" t="n"/>
-      <c r="C13" s="156" t="n"/>
-      <c r="D13" s="156" t="n"/>
-      <c r="E13" s="156" t="n"/>
-      <c r="F13" s="156" t="n"/>
-      <c r="G13" s="156" t="n"/>
-      <c r="H13" s="160" t="n"/>
-      <c r="K13" s="97" t="inlineStr">
+      <c r="L11" s="163" t="n"/>
+      <c r="M11" s="160" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="81">
+      <c r="A12" s="168" t="n"/>
+      <c r="B12" s="165" t="n"/>
+      <c r="C12" s="165" t="n"/>
+      <c r="D12" s="165" t="n"/>
+      <c r="E12" s="165" t="n"/>
+      <c r="F12" s="165" t="n"/>
+      <c r="G12" s="165" t="n"/>
+      <c r="H12" s="169" t="n"/>
+      <c r="K12" s="160" t="n"/>
+      <c r="L12" s="160" t="n"/>
+      <c r="M12" s="160" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="81">
+      <c r="A13" s="168" t="n"/>
+      <c r="B13" s="165" t="n"/>
+      <c r="C13" s="165" t="n"/>
+      <c r="D13" s="165" t="n"/>
+      <c r="E13" s="165" t="n"/>
+      <c r="F13" s="165" t="n"/>
+      <c r="G13" s="165" t="n"/>
+      <c r="H13" s="169" t="n"/>
+      <c r="K13" s="104" t="inlineStr">
         <is>
           <t>Overall Average</t>
         </is>
       </c>
-      <c r="L13" s="100">
+      <c r="L13" s="107">
         <f>IF(COUNT(H5:H39) &gt; 0, ROUND(AVERAGE(H5:H39), 1), "")</f>
         <v/>
       </c>
-      <c r="M13" s="151" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="77">
-      <c r="A14" s="161" t="n"/>
-      <c r="B14" s="156" t="n"/>
-      <c r="C14" s="156" t="n"/>
-      <c r="D14" s="156" t="n"/>
-      <c r="E14" s="156" t="n"/>
-      <c r="F14" s="156" t="n"/>
-      <c r="G14" s="156" t="n"/>
-      <c r="H14" s="162" t="n"/>
-      <c r="K14" s="97" t="inlineStr">
+      <c r="M13" s="160" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="81">
+      <c r="A14" s="170" t="n"/>
+      <c r="B14" s="165" t="n"/>
+      <c r="C14" s="165" t="n"/>
+      <c r="D14" s="165" t="n"/>
+      <c r="E14" s="165" t="n"/>
+      <c r="F14" s="165" t="n"/>
+      <c r="G14" s="165" t="n"/>
+      <c r="H14" s="171" t="n"/>
+      <c r="K14" s="104" t="inlineStr">
         <is>
           <t># Hypoglycemic SMBG</t>
         </is>
       </c>
-      <c r="L14" s="100">
+      <c r="L14" s="107">
         <f>COUNTIF(B5:G39,"&lt;70")</f>
         <v/>
       </c>
-      <c r="M14" s="151" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="77">
-      <c r="A15" s="155" t="inlineStr">
+      <c r="M14" s="160" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="81">
+      <c r="A15" s="164" t="inlineStr">
         <is>
           <t>Before Lunch</t>
         </is>
       </c>
-      <c r="B15" s="156" t="n"/>
-      <c r="C15" s="156" t="n"/>
-      <c r="D15" s="156" t="n"/>
-      <c r="E15" s="156" t="n"/>
-      <c r="F15" s="156" t="n"/>
-      <c r="G15" s="156" t="n"/>
-      <c r="H15" s="100">
+      <c r="B15" s="165" t="n"/>
+      <c r="C15" s="165" t="n"/>
+      <c r="D15" s="165" t="n"/>
+      <c r="E15" s="165" t="n"/>
+      <c r="F15" s="165" t="n"/>
+      <c r="G15" s="165" t="n"/>
+      <c r="H15" s="107">
         <f>IF(COUNT(B15:G19) &gt; 0, ROUND(AVERAGE(B15:G19), 1), "")</f>
         <v/>
       </c>
-      <c r="K15" s="97" t="inlineStr">
+      <c r="K15" s="104" t="inlineStr">
         <is>
           <t># SMBG &gt; 180</t>
         </is>
       </c>
-      <c r="L15" s="100">
+      <c r="L15" s="107">
         <f>COUNTIF(B5:G39, "&gt;180")</f>
         <v/>
       </c>
-      <c r="M15" s="151" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="77">
-      <c r="A16" s="159" t="n"/>
-      <c r="B16" s="156" t="n"/>
-      <c r="C16" s="156" t="n"/>
-      <c r="D16" s="156" t="n"/>
-      <c r="E16" s="156" t="n"/>
-      <c r="F16" s="156" t="n"/>
-      <c r="G16" s="156" t="n"/>
-      <c r="H16" s="160" t="n"/>
-      <c r="K16" s="151" t="n"/>
-      <c r="L16" s="151" t="n"/>
-      <c r="M16" s="151" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="77">
-      <c r="A17" s="159" t="n"/>
-      <c r="B17" s="156" t="n"/>
-      <c r="C17" s="156" t="n"/>
-      <c r="D17" s="156" t="n"/>
-      <c r="E17" s="156" t="n"/>
-      <c r="F17" s="156" t="n"/>
-      <c r="G17" s="156" t="n"/>
-      <c r="H17" s="160" t="n"/>
-      <c r="K17" s="152" t="inlineStr">
+      <c r="M15" s="160" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="81">
+      <c r="A16" s="168" t="n"/>
+      <c r="B16" s="165" t="n"/>
+      <c r="C16" s="165" t="n"/>
+      <c r="D16" s="165" t="n"/>
+      <c r="E16" s="165" t="n"/>
+      <c r="F16" s="165" t="n"/>
+      <c r="G16" s="165" t="n"/>
+      <c r="H16" s="169" t="n"/>
+      <c r="K16" s="160" t="n"/>
+      <c r="L16" s="160" t="n"/>
+      <c r="M16" s="160" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="81">
+      <c r="A17" s="168" t="n"/>
+      <c r="B17" s="165" t="n"/>
+      <c r="C17" s="165" t="n"/>
+      <c r="D17" s="165" t="n"/>
+      <c r="E17" s="165" t="n"/>
+      <c r="F17" s="165" t="n"/>
+      <c r="G17" s="165" t="n"/>
+      <c r="H17" s="169" t="n"/>
+      <c r="K17" s="161" t="inlineStr">
         <is>
           <t>Conversions</t>
         </is>
       </c>
-      <c r="L17" s="164" t="inlineStr">
+      <c r="L17" s="173" t="inlineStr">
         <is>
           <t>Enter</t>
         </is>
       </c>
-      <c r="M17" s="152" t="inlineStr">
+      <c r="M17" s="161" t="inlineStr">
         <is>
           <t>Conversion</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="77">
-      <c r="A18" s="159" t="n"/>
-      <c r="B18" s="156" t="n"/>
-      <c r="C18" s="156" t="n"/>
-      <c r="D18" s="156" t="n"/>
-      <c r="E18" s="156" t="n"/>
-      <c r="F18" s="156" t="n"/>
-      <c r="G18" s="156" t="n"/>
-      <c r="H18" s="160" t="n"/>
-      <c r="K18" s="165" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="81">
+      <c r="A18" s="168" t="n"/>
+      <c r="B18" s="165" t="n"/>
+      <c r="C18" s="165" t="n"/>
+      <c r="D18" s="165" t="n"/>
+      <c r="E18" s="165" t="n"/>
+      <c r="F18" s="165" t="n"/>
+      <c r="G18" s="165" t="n"/>
+      <c r="H18" s="169" t="n"/>
+      <c r="K18" s="174" t="inlineStr">
         <is>
           <t>A1C to estimated glucose</t>
         </is>
       </c>
-      <c r="L18" s="166" t="n"/>
-      <c r="M18" s="100">
+      <c r="L18" s="175" t="n"/>
+      <c r="M18" s="107">
         <f>IF(L18="", "", 28.7*L18-46.7)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="77">
-      <c r="A19" s="161" t="n"/>
-      <c r="B19" s="156" t="n"/>
-      <c r="C19" s="156" t="n"/>
-      <c r="D19" s="156" t="n"/>
-      <c r="E19" s="156" t="n"/>
-      <c r="F19" s="156" t="n"/>
-      <c r="G19" s="156" t="n"/>
-      <c r="H19" s="162" t="n"/>
-      <c r="K19" s="165" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="81">
+      <c r="A19" s="170" t="n"/>
+      <c r="B19" s="165" t="n"/>
+      <c r="C19" s="165" t="n"/>
+      <c r="D19" s="165" t="n"/>
+      <c r="E19" s="165" t="n"/>
+      <c r="F19" s="165" t="n"/>
+      <c r="G19" s="165" t="n"/>
+      <c r="H19" s="171" t="n"/>
+      <c r="K19" s="174" t="inlineStr">
         <is>
           <t>Average glucose to A1c</t>
         </is>
       </c>
-      <c r="L19" s="166" t="n"/>
-      <c r="M19" s="100">
+      <c r="L19" s="175" t="n"/>
+      <c r="M19" s="107">
         <f>IF(L19="", "", ((L19+46.7)/28.7))</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="77">
-      <c r="A20" s="155" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="81">
+      <c r="A20" s="164" t="inlineStr">
         <is>
           <t>After Lunch</t>
         </is>
       </c>
-      <c r="B20" s="156" t="n"/>
-      <c r="C20" s="156" t="n"/>
-      <c r="D20" s="156" t="n"/>
-      <c r="E20" s="156" t="n"/>
-      <c r="F20" s="156" t="n"/>
-      <c r="G20" s="156" t="n"/>
-      <c r="H20" s="100">
+      <c r="B20" s="165" t="n"/>
+      <c r="C20" s="165" t="n"/>
+      <c r="D20" s="165" t="n"/>
+      <c r="E20" s="165" t="n"/>
+      <c r="F20" s="165" t="n"/>
+      <c r="G20" s="165" t="n"/>
+      <c r="H20" s="107">
         <f>IF(COUNT(B20:G24) &gt; 0, ROUND(AVERAGE(B20:G24), 1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="77">
-      <c r="A21" s="159" t="n"/>
-      <c r="B21" s="156" t="n"/>
-      <c r="C21" s="156" t="n"/>
-      <c r="D21" s="156" t="n"/>
-      <c r="E21" s="156" t="n"/>
-      <c r="F21" s="156" t="n"/>
-      <c r="G21" s="156" t="n"/>
-      <c r="H21" s="160" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="77">
-      <c r="A22" s="159" t="n"/>
-      <c r="B22" s="156" t="n"/>
-      <c r="C22" s="156" t="n"/>
-      <c r="D22" s="156" t="n"/>
-      <c r="E22" s="156" t="n"/>
-      <c r="F22" s="156" t="n"/>
-      <c r="G22" s="156" t="n"/>
-      <c r="H22" s="160" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="77">
-      <c r="A23" s="159" t="n"/>
-      <c r="B23" s="156" t="n"/>
-      <c r="C23" s="156" t="n"/>
-      <c r="D23" s="156" t="n"/>
-      <c r="E23" s="156" t="n"/>
-      <c r="F23" s="156" t="n"/>
-      <c r="G23" s="156" t="n"/>
-      <c r="H23" s="160" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="77">
-      <c r="A24" s="161" t="n"/>
-      <c r="B24" s="156" t="n"/>
-      <c r="C24" s="156" t="n"/>
-      <c r="D24" s="156" t="n"/>
-      <c r="E24" s="156" t="n"/>
-      <c r="F24" s="156" t="n"/>
-      <c r="G24" s="156" t="n"/>
-      <c r="H24" s="162" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="77">
-      <c r="A25" s="155" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="81">
+      <c r="A21" s="168" t="n"/>
+      <c r="B21" s="165" t="n"/>
+      <c r="C21" s="165" t="n"/>
+      <c r="D21" s="165" t="n"/>
+      <c r="E21" s="165" t="n"/>
+      <c r="F21" s="165" t="n"/>
+      <c r="G21" s="165" t="n"/>
+      <c r="H21" s="169" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="81">
+      <c r="A22" s="168" t="n"/>
+      <c r="B22" s="165" t="n"/>
+      <c r="C22" s="165" t="n"/>
+      <c r="D22" s="165" t="n"/>
+      <c r="E22" s="165" t="n"/>
+      <c r="F22" s="165" t="n"/>
+      <c r="G22" s="165" t="n"/>
+      <c r="H22" s="169" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="81">
+      <c r="A23" s="168" t="n"/>
+      <c r="B23" s="165" t="n"/>
+      <c r="C23" s="165" t="n"/>
+      <c r="D23" s="165" t="n"/>
+      <c r="E23" s="165" t="n"/>
+      <c r="F23" s="165" t="n"/>
+      <c r="G23" s="165" t="n"/>
+      <c r="H23" s="169" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="81">
+      <c r="A24" s="170" t="n"/>
+      <c r="B24" s="165" t="n"/>
+      <c r="C24" s="165" t="n"/>
+      <c r="D24" s="165" t="n"/>
+      <c r="E24" s="165" t="n"/>
+      <c r="F24" s="165" t="n"/>
+      <c r="G24" s="165" t="n"/>
+      <c r="H24" s="171" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="81">
+      <c r="A25" s="164" t="inlineStr">
         <is>
           <t>Before Dinner</t>
         </is>
       </c>
-      <c r="B25" s="156" t="n"/>
-      <c r="C25" s="156" t="n"/>
-      <c r="D25" s="156" t="n"/>
-      <c r="E25" s="156" t="n"/>
-      <c r="F25" s="156" t="n"/>
-      <c r="G25" s="156" t="n"/>
-      <c r="H25" s="100">
+      <c r="B25" s="165" t="n"/>
+      <c r="C25" s="165" t="n"/>
+      <c r="D25" s="165" t="n"/>
+      <c r="E25" s="165" t="n"/>
+      <c r="F25" s="165" t="n"/>
+      <c r="G25" s="165" t="n"/>
+      <c r="H25" s="107">
         <f>IF(COUNT(B25:G29) &gt; 0, ROUND(AVERAGE(B25:G29), 1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="77">
-      <c r="A26" s="159" t="n"/>
-      <c r="B26" s="156" t="n"/>
-      <c r="C26" s="156" t="n"/>
-      <c r="D26" s="156" t="n"/>
-      <c r="E26" s="156" t="n"/>
-      <c r="F26" s="156" t="n"/>
-      <c r="G26" s="156" t="n"/>
-      <c r="H26" s="160" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="77">
-      <c r="A27" s="159" t="n"/>
-      <c r="B27" s="156" t="n"/>
-      <c r="C27" s="156" t="n"/>
-      <c r="D27" s="156" t="n"/>
-      <c r="E27" s="156" t="n"/>
-      <c r="F27" s="156" t="n"/>
-      <c r="G27" s="156" t="n"/>
-      <c r="H27" s="160" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="77">
-      <c r="A28" s="159" t="n"/>
-      <c r="B28" s="156" t="n"/>
-      <c r="C28" s="156" t="n"/>
-      <c r="D28" s="156" t="n"/>
-      <c r="E28" s="156" t="n"/>
-      <c r="F28" s="156" t="n"/>
-      <c r="G28" s="156" t="n"/>
-      <c r="H28" s="160" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="77">
-      <c r="A29" s="161" t="n"/>
-      <c r="B29" s="156" t="n"/>
-      <c r="C29" s="156" t="n"/>
-      <c r="D29" s="156" t="n"/>
-      <c r="E29" s="156" t="n"/>
-      <c r="F29" s="156" t="n"/>
-      <c r="G29" s="156" t="n"/>
-      <c r="H29" s="162" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="77">
-      <c r="A30" s="155" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="81">
+      <c r="A26" s="168" t="n"/>
+      <c r="B26" s="165" t="n"/>
+      <c r="C26" s="165" t="n"/>
+      <c r="D26" s="165" t="n"/>
+      <c r="E26" s="165" t="n"/>
+      <c r="F26" s="165" t="n"/>
+      <c r="G26" s="165" t="n"/>
+      <c r="H26" s="169" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="81">
+      <c r="A27" s="168" t="n"/>
+      <c r="B27" s="165" t="n"/>
+      <c r="C27" s="165" t="n"/>
+      <c r="D27" s="165" t="n"/>
+      <c r="E27" s="165" t="n"/>
+      <c r="F27" s="165" t="n"/>
+      <c r="G27" s="165" t="n"/>
+      <c r="H27" s="169" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="81">
+      <c r="A28" s="168" t="n"/>
+      <c r="B28" s="165" t="n"/>
+      <c r="C28" s="165" t="n"/>
+      <c r="D28" s="165" t="n"/>
+      <c r="E28" s="165" t="n"/>
+      <c r="F28" s="165" t="n"/>
+      <c r="G28" s="165" t="n"/>
+      <c r="H28" s="169" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="81">
+      <c r="A29" s="170" t="n"/>
+      <c r="B29" s="165" t="n"/>
+      <c r="C29" s="165" t="n"/>
+      <c r="D29" s="165" t="n"/>
+      <c r="E29" s="165" t="n"/>
+      <c r="F29" s="165" t="n"/>
+      <c r="G29" s="165" t="n"/>
+      <c r="H29" s="171" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="81">
+      <c r="A30" s="164" t="inlineStr">
         <is>
           <t>After Dinner</t>
         </is>
       </c>
-      <c r="B30" s="156" t="n"/>
-      <c r="C30" s="156" t="n"/>
-      <c r="D30" s="156" t="n"/>
-      <c r="E30" s="156" t="n"/>
-      <c r="F30" s="156" t="n"/>
-      <c r="G30" s="156" t="n"/>
-      <c r="H30" s="100">
+      <c r="B30" s="165" t="n"/>
+      <c r="C30" s="165" t="n"/>
+      <c r="D30" s="165" t="n"/>
+      <c r="E30" s="165" t="n"/>
+      <c r="F30" s="165" t="n"/>
+      <c r="G30" s="165" t="n"/>
+      <c r="H30" s="107">
         <f>IF(COUNT(B30:G34) &gt; 0, ROUND(AVERAGE(B30:G34), 1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="77">
-      <c r="A31" s="159" t="n"/>
-      <c r="B31" s="156" t="n"/>
-      <c r="C31" s="156" t="n"/>
-      <c r="D31" s="156" t="n"/>
-      <c r="E31" s="156" t="n"/>
-      <c r="F31" s="156" t="n"/>
-      <c r="G31" s="156" t="n"/>
-      <c r="H31" s="160" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="77">
-      <c r="A32" s="159" t="n"/>
-      <c r="B32" s="156" t="n"/>
-      <c r="C32" s="156" t="n"/>
-      <c r="D32" s="156" t="n"/>
-      <c r="E32" s="156" t="n"/>
-      <c r="F32" s="156" t="n"/>
-      <c r="G32" s="156" t="n"/>
-      <c r="H32" s="160" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="77">
-      <c r="A33" s="159" t="n"/>
-      <c r="B33" s="156" t="n"/>
-      <c r="C33" s="156" t="n"/>
-      <c r="D33" s="156" t="n"/>
-      <c r="E33" s="156" t="n"/>
-      <c r="F33" s="156" t="n"/>
-      <c r="G33" s="156" t="n"/>
-      <c r="H33" s="160" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="77">
-      <c r="A34" s="161" t="n"/>
-      <c r="B34" s="156" t="n"/>
-      <c r="C34" s="156" t="n"/>
-      <c r="D34" s="156" t="n"/>
-      <c r="E34" s="156" t="n"/>
-      <c r="F34" s="156" t="n"/>
-      <c r="G34" s="156" t="n"/>
-      <c r="H34" s="162" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="77">
-      <c r="A35" s="155" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="81">
+      <c r="A31" s="168" t="n"/>
+      <c r="B31" s="165" t="n"/>
+      <c r="C31" s="165" t="n"/>
+      <c r="D31" s="165" t="n"/>
+      <c r="E31" s="165" t="n"/>
+      <c r="F31" s="165" t="n"/>
+      <c r="G31" s="165" t="n"/>
+      <c r="H31" s="169" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="81">
+      <c r="A32" s="168" t="n"/>
+      <c r="B32" s="165" t="n"/>
+      <c r="C32" s="165" t="n"/>
+      <c r="D32" s="165" t="n"/>
+      <c r="E32" s="165" t="n"/>
+      <c r="F32" s="165" t="n"/>
+      <c r="G32" s="165" t="n"/>
+      <c r="H32" s="169" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="81">
+      <c r="A33" s="168" t="n"/>
+      <c r="B33" s="165" t="n"/>
+      <c r="C33" s="165" t="n"/>
+      <c r="D33" s="165" t="n"/>
+      <c r="E33" s="165" t="n"/>
+      <c r="F33" s="165" t="n"/>
+      <c r="G33" s="165" t="n"/>
+      <c r="H33" s="169" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="81">
+      <c r="A34" s="170" t="n"/>
+      <c r="B34" s="165" t="n"/>
+      <c r="C34" s="165" t="n"/>
+      <c r="D34" s="165" t="n"/>
+      <c r="E34" s="165" t="n"/>
+      <c r="F34" s="165" t="n"/>
+      <c r="G34" s="165" t="n"/>
+      <c r="H34" s="171" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="81">
+      <c r="A35" s="164" t="inlineStr">
         <is>
           <t>Bedtime</t>
         </is>
       </c>
-      <c r="B35" s="156" t="n"/>
-      <c r="C35" s="156" t="n"/>
-      <c r="D35" s="156" t="n"/>
-      <c r="E35" s="156" t="n"/>
-      <c r="F35" s="156" t="n"/>
-      <c r="G35" s="156" t="n"/>
-      <c r="H35" s="100">
+      <c r="B35" s="165" t="n"/>
+      <c r="C35" s="165" t="n"/>
+      <c r="D35" s="165" t="n"/>
+      <c r="E35" s="165" t="n"/>
+      <c r="F35" s="165" t="n"/>
+      <c r="G35" s="165" t="n"/>
+      <c r="H35" s="107">
         <f>IF(COUNT(B35:G39) &gt; 0, ROUND(AVERAGE(B35:G39), 1), "")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="77">
-      <c r="A36" s="159" t="n"/>
-      <c r="B36" s="156" t="n"/>
-      <c r="C36" s="156" t="n"/>
-      <c r="D36" s="156" t="n"/>
-      <c r="E36" s="156" t="n"/>
-      <c r="F36" s="156" t="n"/>
-      <c r="G36" s="156" t="n"/>
-      <c r="H36" s="160" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="77">
-      <c r="A37" s="159" t="n"/>
-      <c r="B37" s="156" t="n"/>
-      <c r="C37" s="156" t="n"/>
-      <c r="D37" s="156" t="n"/>
-      <c r="E37" s="156" t="n"/>
-      <c r="F37" s="156" t="n"/>
-      <c r="G37" s="156" t="n"/>
-      <c r="H37" s="160" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="77">
-      <c r="A38" s="159" t="n"/>
-      <c r="B38" s="156" t="n"/>
-      <c r="C38" s="156" t="n"/>
-      <c r="D38" s="156" t="n"/>
-      <c r="E38" s="156" t="n"/>
-      <c r="F38" s="156" t="n"/>
-      <c r="G38" s="156" t="n"/>
-      <c r="H38" s="160" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="77">
-      <c r="A39" s="161" t="n"/>
-      <c r="B39" s="156" t="n"/>
-      <c r="C39" s="156" t="n"/>
-      <c r="D39" s="156" t="n"/>
-      <c r="E39" s="156" t="n"/>
-      <c r="F39" s="156" t="n"/>
-      <c r="G39" s="156" t="n"/>
-      <c r="H39" s="162" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1" s="77">
-      <c r="A41" s="167" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="81">
+      <c r="A36" s="168" t="n"/>
+      <c r="B36" s="165" t="n"/>
+      <c r="C36" s="165" t="n"/>
+      <c r="D36" s="165" t="n"/>
+      <c r="E36" s="165" t="n"/>
+      <c r="F36" s="165" t="n"/>
+      <c r="G36" s="165" t="n"/>
+      <c r="H36" s="169" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="81">
+      <c r="A37" s="168" t="n"/>
+      <c r="B37" s="165" t="n"/>
+      <c r="C37" s="165" t="n"/>
+      <c r="D37" s="165" t="n"/>
+      <c r="E37" s="165" t="n"/>
+      <c r="F37" s="165" t="n"/>
+      <c r="G37" s="165" t="n"/>
+      <c r="H37" s="169" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="81">
+      <c r="A38" s="168" t="n"/>
+      <c r="B38" s="165" t="n"/>
+      <c r="C38" s="165" t="n"/>
+      <c r="D38" s="165" t="n"/>
+      <c r="E38" s="165" t="n"/>
+      <c r="F38" s="165" t="n"/>
+      <c r="G38" s="165" t="n"/>
+      <c r="H38" s="169" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="81">
+      <c r="A39" s="170" t="n"/>
+      <c r="B39" s="165" t="n"/>
+      <c r="C39" s="165" t="n"/>
+      <c r="D39" s="165" t="n"/>
+      <c r="E39" s="165" t="n"/>
+      <c r="F39" s="165" t="n"/>
+      <c r="G39" s="165" t="n"/>
+      <c r="H39" s="171" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="81">
+      <c r="A41" s="176" t="inlineStr">
         <is>
           <t>ADDITIONAL 2026 ADA TARGETS  —  new</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1" s="77">
-      <c r="A42" s="119" t="inlineStr">
+    <row r="42" ht="30" customHeight="1" s="81">
+      <c r="A42" s="126" t="inlineStr">
         <is>
           <t>Glycemic and CGM targets are now framed more explicitly around age, frailty, and functional/health status rather than a single flat number — individualize the &lt;7% A1C goal accordingly, especially in older adults (ADA 2026, Sections 6 and 13).</t>
         </is>
       </c>
-      <c r="B42" s="150" t="n"/>
-      <c r="C42" s="150" t="n"/>
-      <c r="D42" s="150" t="n"/>
-      <c r="E42" s="150" t="n"/>
-      <c r="F42" s="150" t="n"/>
-      <c r="G42" s="150" t="n"/>
-      <c r="H42" s="150" t="n"/>
-      <c r="I42" s="150" t="n"/>
-      <c r="J42" s="150" t="n"/>
-      <c r="K42" s="150" t="n"/>
-      <c r="L42" s="150" t="n"/>
-      <c r="M42" s="120" t="n"/>
-    </row>
-    <row r="43" ht="30" customHeight="1" s="77">
-      <c r="A43" s="119" t="inlineStr">
+      <c r="B42" s="159" t="n"/>
+      <c r="C42" s="159" t="n"/>
+      <c r="D42" s="159" t="n"/>
+      <c r="E42" s="159" t="n"/>
+      <c r="F42" s="159" t="n"/>
+      <c r="G42" s="159" t="n"/>
+      <c r="H42" s="159" t="n"/>
+      <c r="I42" s="159" t="n"/>
+      <c r="J42" s="159" t="n"/>
+      <c r="K42" s="159" t="n"/>
+      <c r="L42" s="159" t="n"/>
+      <c r="M42" s="127" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1" s="81">
+      <c r="A43" s="126" t="inlineStr">
         <is>
           <t>New perioperative target (ADA 2026): A1C ≤ 8% before elective surgery; inpatient glucose 100-180 mg/dL before, during, and after surgery.</t>
         </is>
       </c>
-      <c r="B43" s="150" t="n"/>
-      <c r="C43" s="150" t="n"/>
-      <c r="D43" s="150" t="n"/>
-      <c r="E43" s="150" t="n"/>
-      <c r="F43" s="150" t="n"/>
-      <c r="G43" s="150" t="n"/>
-      <c r="H43" s="150" t="n"/>
-      <c r="I43" s="150" t="n"/>
-      <c r="J43" s="150" t="n"/>
-      <c r="K43" s="150" t="n"/>
-      <c r="L43" s="150" t="n"/>
-      <c r="M43" s="120" t="n"/>
-    </row>
-    <row r="45" ht="30" customHeight="1" s="77">
-      <c r="A45" s="129" t="inlineStr">
+      <c r="B43" s="159" t="n"/>
+      <c r="C43" s="159" t="n"/>
+      <c r="D43" s="159" t="n"/>
+      <c r="E43" s="159" t="n"/>
+      <c r="F43" s="159" t="n"/>
+      <c r="G43" s="159" t="n"/>
+      <c r="H43" s="159" t="n"/>
+      <c r="I43" s="159" t="n"/>
+      <c r="J43" s="159" t="n"/>
+      <c r="K43" s="159" t="n"/>
+      <c r="L43" s="159" t="n"/>
+      <c r="M43" s="127" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1" s="81">
+      <c r="A45" s="136" t="inlineStr">
         <is>
           <t>Source: American Diabetes Association. Standards of Care in Diabetes—2026. Diabetes Care. 2026;49(Suppl 1), Sections 6 and 13. Core fasting/postprandial/hypoglycemia numeric thresholds (80-130, &lt;180, &lt;70 mg/dL) verified as carryover with no confirmed 2026 numeric change; cross-check Table 6.2 directly if this tool is used for a non-standard target population.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="a80f"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="25">
     <mergeCell ref="A5:A9"/>
     <mergeCell ref="A20:A24"/>
